--- a/@output/Chunks_LMS_Green_Red_Reused_Improv.xlsx
+++ b/@output/Chunks_LMS_Green_Red_Reused_Improv.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,12 +60,18 @@
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <name val="Consolas"/>
       <color rgb="000F172A"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -88,6 +94,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00059669"/>
         <bgColor rgb="00059669"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECFDF5"/>
+        <bgColor rgb="00ECFDF5"/>
       </patternFill>
     </fill>
     <fill>
@@ -123,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -157,13 +169,19 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -816,7 +834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
@@ -827,12 +845,14 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="41" customWidth="1" min="9" max="9"/>
-    <col width="38" customWidth="1" min="10" max="10"/>
-    <col width="65" customWidth="1" min="11" max="11"/>
-    <col width="65" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="41" customWidth="1" min="11" max="11"/>
+    <col width="38" customWidth="1" min="12" max="12"/>
+    <col width="65" customWidth="1" min="13" max="13"/>
+    <col width="65" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="25" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -845,7 +865,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fluent Complete Sentences (TL = 1.0) • Target CPD 12V • Per-Session TTS Audio</t>
+          <t>Fluent Complete Sentences (TL = 1.0) • Target CPD 12V • Linear VI Word Count Progression (S1: 10w → S7: 22w max)</t>
         </is>
       </c>
     </row>
@@ -893,30 +913,40 @@
       </c>
       <c r="I4" s="12" t="inlineStr">
         <is>
+          <t>VI Word Count</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>Target Progression</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
           <t>Term (EN)</t>
         </is>
       </c>
-      <c r="J4" s="12" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
         <is>
           <t>Term (VI)</t>
         </is>
       </c>
-      <c r="K4" s="12" t="inlineStr">
+      <c r="M4" s="12" t="inlineStr">
         <is>
           <t>Complete Sentence (EN)</t>
         </is>
       </c>
-      <c r="L4" s="12" t="inlineStr">
+      <c r="N4" s="12" t="inlineStr">
         <is>
           <t>Complete Sentence (VI)</t>
         </is>
       </c>
-      <c r="M4" s="12" t="inlineStr">
+      <c r="O4" s="12" t="inlineStr">
         <is>
           <t>Audio Lang</t>
         </is>
       </c>
-      <c r="N4" s="12" t="inlineStr">
+      <c r="P4" s="12" t="inlineStr">
         <is>
           <t>Voice Model</t>
         </is>
@@ -951,32 +981,42 @@
       <c r="H5" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>10 từ</t>
+        </is>
+      </c>
+      <c r="J5" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (9-10w)</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>E-commerce industry</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>Ngành thương mại điện tử</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>The e-commerce industry is fiercely competitive in this modern market.</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>Ngành thương mại điện tử cạnh tranh rất khốc liệt trong thị trường hiện đại.</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>The e-commerce industry is fiercely competitive in modern markets.</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>Ngành thương mại điện tử cạnh tranh rất khốc liệt.</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="P5" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -1011,32 +1051,42 @@
       <c r="H6" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>10 từ</t>
+        </is>
+      </c>
+      <c r="J6" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (9-10w)</t>
+        </is>
+      </c>
+      <c r="K6" s="11" t="inlineStr">
         <is>
           <t>Midnight deal hunting</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="L6" s="11" t="inlineStr">
         <is>
           <t>Săn sale nửa đêm</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
-        <is>
-          <t>Many online shoppers stay up late for midnight deal hunting.</t>
-        </is>
-      </c>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>Nhiều người mua sắm trực tuyến thức trắng đêm để săn sale nửa đêm.</t>
-        </is>
-      </c>
-      <c r="M6" s="9" t="inlineStr">
+      <c r="M6" s="11" t="inlineStr">
+        <is>
+          <t>Many shoppers stay up late for midnight discount sales.</t>
+        </is>
+      </c>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>Nhiều người thức trắng đêm để săn sale giảm giá.</t>
+        </is>
+      </c>
+      <c r="O6" s="9" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="N6" s="11" t="inlineStr">
+      <c r="P6" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -1071,32 +1121,42 @@
       <c r="H7" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>10 từ</t>
+        </is>
+      </c>
+      <c r="J7" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (9-10w)</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>Linked digital wallet</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>Ví điện tử liên kết</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>My digital wallet is securely linked to my local bank account.</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>Ví điện tử của tôi đã được liên kết an toàn với tài khoản ngân hàng.</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>The digital wallet is safely linked to bank accounts.</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>Ví điện tử đã được liên kết với ngân hàng.</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr">
+      <c r="P7" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -1131,32 +1191,42 @@
       <c r="H8" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="I8" s="11" t="inlineStr">
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>12 từ</t>
+        </is>
+      </c>
+      <c r="J8" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (11-12w)</t>
+        </is>
+      </c>
+      <c r="K8" s="11" t="inlineStr">
         <is>
           <t>Competitive pricing</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="L8" s="11" t="inlineStr">
         <is>
           <t>Mức giá cạnh tranh</t>
         </is>
       </c>
-      <c r="K8" s="11" t="inlineStr">
-        <is>
-          <t>Competitive pricing always helps new online stores draw customers.</t>
-        </is>
-      </c>
-      <c r="L8" s="11" t="inlineStr">
-        <is>
-          <t>Mức giá cạnh tranh luôn giúp các cửa hàng trực tuyến thu hút khách mua.</t>
-        </is>
-      </c>
-      <c r="M8" s="9" t="inlineStr">
+      <c r="M8" s="11" t="inlineStr">
+        <is>
+          <t>Competitive pricing always helps retail shops draw active customers.</t>
+        </is>
+      </c>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>Mức giá cạnh tranh luôn giúp cửa hàng thu hút khách mua.</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="N8" s="11" t="inlineStr">
+      <c r="P8" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -1191,32 +1261,42 @@
       <c r="H9" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>12 từ</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (11-12w)</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
         <is>
           <t>Casual window shopping</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="L9" s="7" t="inlineStr">
         <is>
           <t>Dạo ngắm đồ online</t>
         </is>
       </c>
-      <c r="K9" s="7" t="inlineStr">
-        <is>
-          <t>I often enjoy casual window shopping on mobile apps to unwind after work.</t>
-        </is>
-      </c>
-      <c r="L9" s="7" t="inlineStr">
-        <is>
-          <t>Tôi thường dạo ngắm đồ trên ứng dụng điện thoại để xả stress sau giờ làm.</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>I often enjoy casual window shopping online to relieve stress.</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>Tôi thường dạo ngắm đồ trên mạng để giải tỏa căng thẳng.</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="N9" s="7" t="inlineStr">
+      <c r="P9" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -1251,32 +1331,42 @@
       <c r="H10" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>12 từ</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (11-12w)</t>
+        </is>
+      </c>
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Overflowing shopping cart</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Giỏ hàng đầy ắp</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
-        <is>
-          <t>Her virtual shopping cart is already overflowing with seasonal discounts.</t>
-        </is>
-      </c>
-      <c r="L10" s="11" t="inlineStr">
-        <is>
-          <t>Giỏ hàng trực tuyến của cô ấy đã đầy ắp các món đồ giảm giá theo mùa.</t>
-        </is>
-      </c>
-      <c r="M10" s="9" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
+        <is>
+          <t>Her virtual shopping cart is overflowing with great discounted products.</t>
+        </is>
+      </c>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>Giỏ hàng trực tuyến của cô ấy đầy ắp đồ giảm giá.</t>
+        </is>
+      </c>
+      <c r="O10" s="9" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="P10" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -1311,32 +1401,42 @@
       <c r="H11" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>14 từ</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (13-14w)</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
         <is>
           <t>Flash sale drive</t>
         </is>
       </c>
-      <c r="J11" s="7" t="inlineStr">
+      <c r="L11" s="7" t="inlineStr">
         <is>
           <t>Chiến dịch săn sale</t>
         </is>
       </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>The platform hyped up the flash sale drive, so millions of shoppers joined early.</t>
-        </is>
-      </c>
-      <c r="L11" s="7" t="inlineStr">
-        <is>
-          <t>Nền tảng đã quảng bá rầm rộ chiến dịch săn sale, vì thế hàng triệu người tham gia từ sớm.</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>The flash sale was hyped up, so customers placed orders very early.</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>Chiến dịch săn sale được quảng bá rầm rộ nên khách đặt mua sớm.</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="N11" s="7" t="inlineStr">
+      <c r="P11" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -1371,32 +1471,42 @@
       <c r="H12" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>14 từ</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (13-14w)</t>
+        </is>
+      </c>
+      <c r="K12" s="11" t="inlineStr">
         <is>
           <t>E-wallet checkout</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="L12" s="11" t="inlineStr">
         <is>
           <t>Thanh toán ví điện tử</t>
         </is>
       </c>
-      <c r="K12" s="11" t="inlineStr">
-        <is>
-          <t>You should complete your e-wallet checkout today, and you will get instant cashback.</t>
-        </is>
-      </c>
-      <c r="L12" s="11" t="inlineStr">
-        <is>
-          <t>Bạn nên hoàn tất thanh toán bằng ví điện tử hôm nay, và bạn sẽ nhận được tiền hoàn ngay lập tức.</t>
-        </is>
-      </c>
-      <c r="M12" s="9" t="inlineStr">
+      <c r="M12" s="11" t="inlineStr">
+        <is>
+          <t>When checking out with an e-wallet, you receive cashback instantly.</t>
+        </is>
+      </c>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>Khi thanh toán bằng ví điện tử, bạn sẽ nhận được tiền hoàn ngay.</t>
+        </is>
+      </c>
+      <c r="O12" s="9" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="N12" s="11" t="inlineStr">
+      <c r="P12" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -1431,32 +1541,42 @@
       <c r="H13" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>14 từ</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (13-14w)</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
         <is>
           <t>Items in cart</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="L13" s="7" t="inlineStr">
         <is>
           <t>Sản phẩm trong giỏ hàng</t>
         </is>
       </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>Review the items in your cart carefully, as long as they are still in stock.</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>Hãy kiểm tra kỹ các sản phẩm trong giỏ hàng, miễn là chúng vẫn còn đủ số lượng.</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>Check your shopping cart carefully while selected items are still in stock.</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>Bạn nên kiểm tra giỏ hàng cẩn thận khi sản phẩm còn đủ hàng.</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="N13" s="7" t="inlineStr">
+      <c r="P13" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -1491,32 +1611,42 @@
       <c r="H14" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="I14" s="11" t="inlineStr">
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>16 từ</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (15-16w)</t>
+        </is>
+      </c>
+      <c r="K14" s="11" t="inlineStr">
         <is>
           <t>Cashless payments</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="L14" s="11" t="inlineStr">
         <is>
           <t>Thanh toán không tiền mặt</t>
         </is>
       </c>
-      <c r="K14" s="11" t="inlineStr">
-        <is>
-          <t>Cashless payments are supremely convenient, and modern consumers increasingly prefer them.</t>
-        </is>
-      </c>
-      <c r="L14" s="11" t="inlineStr">
-        <is>
-          <t>Phương thức thanh toán không tiền mặt rất tiện lợi, và người tiêu dùng ngày càng ưa chuộng nó.</t>
-        </is>
-      </c>
-      <c r="M14" s="9" t="inlineStr">
+      <c r="M14" s="11" t="inlineStr">
+        <is>
+          <t>Cashless payments are very convenient, so consumers increasingly prefer shopping online.</t>
+        </is>
+      </c>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>Thanh toán không tiền mặt rất thuận tiện, nên người dùng ngày càng chuộng mua sắm.</t>
+        </is>
+      </c>
+      <c r="O14" s="9" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="N14" s="11" t="inlineStr">
+      <c r="P14" s="11" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -1551,32 +1681,42 @@
       <c r="H15" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>16 từ</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (15-16w)</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
         <is>
           <t>Free shipping coupon</t>
         </is>
       </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="L15" s="7" t="inlineStr">
         <is>
           <t>Mã miễn phí vận chuyển</t>
         </is>
       </c>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>The shop offers a free shipping coupon, so customers quickly place more orders.</t>
-        </is>
-      </c>
-      <c r="L15" s="7" t="inlineStr">
-        <is>
-          <t>Cửa hàng tặng kèm mã miễn phí vận chuyển, do đó khách hàng nhanh chóng đặt thêm nhiều đơn mới.</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>The store offers free shipping codes, helping buyers quickly place more orders.</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>Cửa hàng tặng mã miễn phí vận chuyển, giúp khách nhanh chóng chốt thêm nhiều đơn.</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="N15" s="7" t="inlineStr">
+      <c r="P15" s="7" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -1611,32 +1751,42 @@
       <c r="H16" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="I16" s="11" t="inlineStr">
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>16 từ</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (15-16w)</t>
+        </is>
+      </c>
+      <c r="K16" s="11" t="inlineStr">
         <is>
           <t>Instant delivery</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr">
+      <c r="L16" s="11" t="inlineStr">
         <is>
           <t>Giao hàng hỏa tốc</t>
         </is>
       </c>
-      <c r="K16" s="11" t="inlineStr">
-        <is>
-          <t>Instant delivery service is highly popular, but the company must expand nationwide.</t>
-        </is>
-      </c>
-      <c r="L16" s="11" t="inlineStr">
-        <is>
-          <t>Dịch vụ giao hàng hỏa tốc đang rất được yêu thích, nhưng công ty cần mở rộng trên toàn quốc.</t>
-        </is>
-      </c>
-      <c r="M16" s="9" t="inlineStr">
+      <c r="M16" s="11" t="inlineStr">
+        <is>
+          <t>Instant delivery service is great, but companies need to expand their network.</t>
+        </is>
+      </c>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>Dịch vụ giao hàng hỏa tốc rất tốt, nhưng doanh nghiệp cần mở rộng mạng lưới.</t>
+        </is>
+      </c>
+      <c r="O16" s="9" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="N16" s="11" t="inlineStr">
+      <c r="P16" s="11" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -1671,32 +1821,42 @@
       <c r="H17" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>18 từ</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (17-18w)</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
         <is>
           <t>Funnel optimization</t>
         </is>
       </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="L17" s="7" t="inlineStr">
         <is>
           <t>Tối ưu phễu bán hàng</t>
         </is>
       </c>
-      <c r="K17" s="7" t="inlineStr">
-        <is>
-          <t>Although advertising costs have risen, systematically optimizing the sales funnel helped the brand double its revenue.</t>
-        </is>
-      </c>
-      <c r="L17" s="7" t="inlineStr">
-        <is>
-          <t>Mặc dù chi phí quảng cáo tăng cao, việc tối ưu phễu chuyển đổi bài bản đã giúp doanh nghiệp nhân đôi doanh số.</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>Although advertising costs have risen, sales funnel optimization helps significantly increase revenue.</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>Dù chi phí quảng cáo tăng cao, việc tối ưu phễu bán hàng giúp tăng mạnh doanh thu.</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="N17" s="7" t="inlineStr">
+      <c r="P17" s="7" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -1731,32 +1891,42 @@
       <c r="H18" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="I18" s="11" t="inlineStr">
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>18 từ</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (17-18w)</t>
+        </is>
+      </c>
+      <c r="K18" s="11" t="inlineStr">
         <is>
           <t>Loyalty rewards</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="L18" s="11" t="inlineStr">
         <is>
           <t>Chương trình tri ân khách hàng</t>
         </is>
       </c>
-      <c r="K18" s="11" t="inlineStr">
-        <is>
-          <t>By providing attractive loyalty rewards, the brand can successfully retain its valuable customer base over the long run.</t>
-        </is>
-      </c>
-      <c r="L18" s="11" t="inlineStr">
-        <is>
-          <t>Bằng cách cung cấp các chương trình tích điểm tri ân hấp dẫn, thương hiệu có thể giữ chân lượng khách hàng trung thành dài lâu.</t>
-        </is>
-      </c>
-      <c r="M18" s="9" t="inlineStr">
+      <c r="M18" s="11" t="inlineStr">
+        <is>
+          <t>By applying attractive loyalty programs, the brand successfully retained many regular customers.</t>
+        </is>
+      </c>
+      <c r="N18" s="11" t="inlineStr">
+        <is>
+          <t>Nhờ áp dụng chương trình tri ân hấp dẫn, thương hiệu đã giữ chân được nhiều khách quen.</t>
+        </is>
+      </c>
+      <c r="O18" s="9" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="N18" s="11" t="inlineStr">
+      <c r="P18" s="11" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -1791,32 +1961,42 @@
       <c r="H19" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>18 từ</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (17-18w)</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
         <is>
           <t>Shopping frenzy</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="L19" s="7" t="inlineStr">
         <is>
           <t>Cơn sốt mua sắm</t>
         </is>
       </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>When the midnight shopping frenzy suddenly erupted, the engineering team had to monitor continuously so that the servers would not crash.</t>
-        </is>
-      </c>
-      <c r="L19" s="7" t="inlineStr">
-        <is>
-          <t>Khi cơn sốt mua sắm nửa đêm bất ngờ bùng nổ, đội ngũ kỹ thuật phải ứng trực liên tục để hệ thống máy chủ không bị sập.</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>When the shopping frenzy erupted, engineers monitored servers all night to keep them running.</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>Khi cơn sốt mua sắm bùng nổ, các kỹ sư phải túc trực đêm để giữ máy chủ.</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="N19" s="7" t="inlineStr">
+      <c r="P19" s="7" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -1851,32 +2031,42 @@
       <c r="H20" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="I20" s="11" t="inlineStr">
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>20 từ</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (19-20w)</t>
+        </is>
+      </c>
+      <c r="K20" s="11" t="inlineStr">
         <is>
           <t>Conversion rate</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="L20" s="11" t="inlineStr">
         <is>
           <t>Tỉ lệ chuyển đổi đơn</t>
         </is>
       </c>
-      <c r="K20" s="11" t="inlineStr">
-        <is>
-          <t>In e-commerce operations, the checkout conversion rate serves as the vital metric that determines overall financial viability.</t>
-        </is>
-      </c>
-      <c r="L20" s="11" t="inlineStr">
-        <is>
-          <t>Trong kinh doanh thương mại điện tử, tỉ lệ chuyển đổi đơn hàng là thước đo sống còn quyết định toàn bộ hiệu quả tài chính.</t>
-        </is>
-      </c>
-      <c r="M20" s="9" t="inlineStr">
+      <c r="M20" s="11" t="inlineStr">
+        <is>
+          <t>In e-commerce, the checkout conversion rate is a vital metric that determines overall business success.</t>
+        </is>
+      </c>
+      <c r="N20" s="11" t="inlineStr">
+        <is>
+          <t>Trong thương mại điện tử, tỉ lệ chuyển đổi là thước đo sống còn quyết định toàn bộ thành công.</t>
+        </is>
+      </c>
+      <c r="O20" s="9" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="N20" s="11" t="inlineStr">
+      <c r="P20" s="11" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -1911,32 +2101,42 @@
       <c r="H21" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>19 từ</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (19-20w)</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
         <is>
           <t>Express shipping fee</t>
         </is>
       </c>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>Phí giao hàng quá mức</t>
         </is>
       </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>If brands impose excessive express delivery fees, it becomes a major stumbling block that prompts immediate cart abandonment.</t>
-        </is>
-      </c>
-      <c r="L21" s="7" t="inlineStr">
-        <is>
-          <t>Nếu thương hiệu áp đặt phí vận chuyển quá đắt đỏ, điều đó sẽ trở thành rào cản lớn khiến khách hàng lập tức bỏ quên giỏ hàng.</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>If sellers charge excessive shipping fees, customers will immediately abandon their shopping carts.</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>Nếu người bán tính phí vận chuyển quá đắt đỏ, khách hàng sẽ lập tức từ bỏ giỏ hàng.</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="N21" s="7" t="inlineStr">
+      <c r="P21" s="7" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -1971,32 +2171,42 @@
       <c r="H22" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="I22" s="11" t="inlineStr">
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>20 từ</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (19-20w)</t>
+        </is>
+      </c>
+      <c r="K22" s="11" t="inlineStr">
         <is>
           <t>Return guarantee</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="L22" s="11" t="inlineStr">
         <is>
           <t>Chính sách đổi trả minh bạch</t>
         </is>
       </c>
-      <c r="K22" s="11" t="inlineStr">
-        <is>
-          <t>A transparent seven-day return guarantee not only establishes robust consumer trust, but also provides total peace of mind before checkout.</t>
-        </is>
-      </c>
-      <c r="L22" s="11" t="inlineStr">
-        <is>
-          <t>Chính sách đổi trả minh bạch trong bảy ngày không chỉ tạo dựng niềm tin vững chắc, mà còn giúp người mua hoàn toàn yên tâm chốt đơn.</t>
-        </is>
-      </c>
-      <c r="M22" s="9" t="inlineStr">
+      <c r="M22" s="11" t="inlineStr">
+        <is>
+          <t>A seven-day return policy not only builds reputation, but also gives buyers great peace of mind.</t>
+        </is>
+      </c>
+      <c r="N22" s="11" t="inlineStr">
+        <is>
+          <t>Chính sách đổi trả bảy ngày không chỉ tạo dựng uy tín, mà còn giúp khách hàng rất an tâm.</t>
+        </is>
+      </c>
+      <c r="O22" s="9" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="N22" s="11" t="inlineStr">
+      <c r="P22" s="11" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -2031,32 +2241,42 @@
       <c r="H23" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>22 từ</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (21-22w (max))</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
         <is>
           <t>Cash-burning war &amp; market share</t>
         </is>
       </c>
-      <c r="J23" s="7" t="inlineStr">
+      <c r="L23" s="7" t="inlineStr">
         <is>
           <t>Cuộc chiến đốt tiền thị phần</t>
         </is>
       </c>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>While the e-commerce arena remains a highly lucrative market, entering an unsustainable cash-burning war will inevitably drain your capital reserves.</t>
-        </is>
-      </c>
-      <c r="L23" s="7" t="inlineStr">
-        <is>
-          <t>Mặc dù thị trường thương mại điện tử là một miếng bánh vô cùng màu mỡ, việc bước vào cuộc chiến đốt tiền không bền vững chắc chắn sẽ làm cạn kiệt nguồn vốn dự trữ.</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>The retail market is lucrative, but continuous cash burning will inevitably drain an enterprise of capital reserves.</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>Thị trường thương mại rất màu mỡ, nhưng nếu liên tục đốt tiền thì doanh nghiệp sẽ sớm cạn kiệt nguồn vốn.</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="N23" s="7" t="inlineStr">
+      <c r="P23" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -2091,32 +2311,42 @@
       <c r="H24" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="I24" s="11" t="inlineStr">
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>22 từ</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (21-22w (max))</t>
+        </is>
+      </c>
+      <c r="K24" s="11" t="inlineStr">
         <is>
           <t>Live shopping show &amp; checkout velocity</t>
         </is>
       </c>
-      <c r="J24" s="11" t="inlineStr">
+      <c r="L24" s="11" t="inlineStr">
         <is>
           <t>Phiên livestream bán hàng tương tác</t>
         </is>
       </c>
-      <c r="K24" s="11" t="inlineStr">
-        <is>
-          <t>By integrating interactive live shopping shows directly into the platform, retail merchants can captivate impulsive shoppers and achieve extraordinary checkout velocity.</t>
-        </is>
-      </c>
-      <c r="L24" s="11" t="inlineStr">
-        <is>
-          <t>Bằng cách tích hợp các phiên livestream bán hàng tương tác trực tiếp lên nền tảng, nhà bán lẻ có thể thu hút khách mua sắm tùy hứng và đạt tốc độ chốt đơn vượt bậc.</t>
-        </is>
-      </c>
-      <c r="M24" s="9" t="inlineStr">
+      <c r="M24" s="11" t="inlineStr">
+        <is>
+          <t>Hosting live sales streams directly on apps attracts shoppers and achieves remarkably rapid checkout speeds.</t>
+        </is>
+      </c>
+      <c r="N24" s="11" t="inlineStr">
+        <is>
+          <t>Việc tổ chức livestream bán hàng trực tiếp trên ứng dụng giúp thu hút khách mua và chốt đơn rất nhanh chóng.</t>
+        </is>
+      </c>
+      <c r="O24" s="9" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="N24" s="11" t="inlineStr">
+      <c r="P24" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -2151,32 +2381,42 @@
       <c r="H25" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>21 từ</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (21-22w (max))</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
         <is>
           <t>Omnichannel customer retention</t>
         </is>
       </c>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>Chiến lược giữ chân đa kênh</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="inlineStr">
-        <is>
-          <t>To thrive amid aggressive price competition, retail brands must cultivate an omnichannel presence that reinforces customer loyalty and safeguards long-term profit margins.</t>
-        </is>
-      </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>Để phát triển bền vững trước cuộc cạnh tranh giá khốc liệt, các thương hiệu bán lẻ phải xây dựng mô hình đa kênh giúp gia tăng lòng trung thành và bảo vệ biên lợi nhuận dài hạn.</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
+          <t>Chiến lược bán lẻ đa kênh</t>
+        </is>
+      </c>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>To compete effectively in digital markets, retail brands must build sustainable omnichannel sales models.</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="inlineStr">
+        <is>
+          <t>Để cạnh tranh trên thị trường số, các thương hiệu cần xây dựng mô hình bán lẻ đa kênh bền vững.</t>
+        </is>
+      </c>
+      <c r="O25" s="5" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="N25" s="7" t="inlineStr">
+      <c r="P25" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -2188,6 +2428,1605 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="65" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="11" max="11"/>
+    <col width="37" customWidth="1" min="12" max="12"/>
+    <col width="65" customWidth="1" min="13" max="13"/>
+    <col width="65" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="25" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>G02-21Q-Ecommerce-2 — G02-21Q-Ecommerce: E-commerce Market Dynamics &amp; Shopping Reflex (Focus 12V)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Fluent Complete Sentences (TL = 1.0) • Target CPD 12V • Linear VI Word Count Progression (S1: 10w → S7: 22w max)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Session</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Global #</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>CVR (Ω)</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>CCI (A)</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>CPD (V)</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>VI Word Count</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>Target Progression</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>Term (EN)</t>
+        </is>
+      </c>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>Term (VI)</t>
+        </is>
+      </c>
+      <c r="M4" s="12" t="inlineStr">
+        <is>
+          <t>Complete Sentence (EN)</t>
+        </is>
+      </c>
+      <c r="N4" s="12" t="inlineStr">
+        <is>
+          <t>Complete Sentence (VI)</t>
+        </is>
+      </c>
+      <c r="O4" s="12" t="inlineStr">
+        <is>
+          <t>Audio Lang</t>
+        </is>
+      </c>
+      <c r="P4" s="12" t="inlineStr">
+        <is>
+          <t>Voice Model</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Part 1</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>A2 (Simple Sentence)</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>10 từ</t>
+        </is>
+      </c>
+      <c r="J5" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (9-10w)</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>Impulsive shopper</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>Người tiêu dùng tùy hứng</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>An impulsive shopper often picks items based on pure emotion.</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>Người mua tùy hứng thường chọn đồ theo cảm xúc.</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t>google/en-US-Neural2-F</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Part 1</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>A2 (Simple Sentence)</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>10 từ</t>
+        </is>
+      </c>
+      <c r="J6" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (9-10w)</t>
+        </is>
+      </c>
+      <c r="K6" s="11" t="inlineStr">
+        <is>
+          <t>Vibrant marketplace</t>
+        </is>
+      </c>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>Thị trường sôi động</t>
+        </is>
+      </c>
+      <c r="M6" s="11" t="inlineStr">
+        <is>
+          <t>This retail marketplace continues to grow at an extraordinary speed.</t>
+        </is>
+      </c>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>Thị trường bán lẻ này tăng trưởng vô cùng nhanh.</t>
+        </is>
+      </c>
+      <c r="O6" s="9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="P6" s="11" t="inlineStr">
+        <is>
+          <t>google/en-US-Neural2-F</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Part 1</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>A2 (Simple Sentence)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>10 từ</t>
+        </is>
+      </c>
+      <c r="J7" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (9-10w)</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>Secure checkout process</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>Quy trình thanh toán an toàn</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>A secure checkout process helps you feel completely confident.</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>Quy trình thanh toán an toàn giúp bạn an tâm.</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>google/en-US-Neural2-F</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Part 1</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>A2 (Simple Sentence)</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>12 từ</t>
+        </is>
+      </c>
+      <c r="J8" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (11-12w)</t>
+        </is>
+      </c>
+      <c r="K8" s="11" t="inlineStr">
+        <is>
+          <t>Track package in real time</t>
+        </is>
+      </c>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>Theo dõi đơn hàng thời gian thực</t>
+        </is>
+      </c>
+      <c r="M8" s="11" t="inlineStr">
+        <is>
+          <t>Customers can easily track their package journey on mobile phones.</t>
+        </is>
+      </c>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>Khách hàng dễ dàng theo dõi hành trình đơn trên điện thoại.</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="P8" s="11" t="inlineStr">
+        <is>
+          <t>google/en-US-Neural2-F</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Part 1</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>A2 (Simple Sentence)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>12 từ</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (11-12w)</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Genuine product reviews</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>Đánh giá sản phẩm uy tín</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>Reading genuine product reviews helps shoppers choose reputable online stores.</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>Đọc nhận xét thực tế giúp chọn được cửa hàng uy tín.</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>google/en-US-Neural2-F</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Part 1</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>A2 (Simple Sentence)</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>12 từ</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (11-12w)</t>
+        </is>
+      </c>
+      <c r="K10" s="11" t="inlineStr">
+        <is>
+          <t>Discount voucher code</t>
+        </is>
+      </c>
+      <c r="L10" s="11" t="inlineStr">
+        <is>
+          <t>Mã giảm giá ưu đãi</t>
+        </is>
+      </c>
+      <c r="M10" s="11" t="inlineStr">
+        <is>
+          <t>Do not forget to apply your discount voucher before confirming your order.</t>
+        </is>
+      </c>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>Đừng quên nhập mã giảm giá trước khi bạn xác nhận đơn.</t>
+        </is>
+      </c>
+      <c r="O10" s="9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="P10" s="11" t="inlineStr">
+        <is>
+          <t>google/en-US-Neural2-F</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Part 2</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>B1 (Compound Sentence)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>14 từ</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (13-14w)</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>Impulsive shoppers</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>Khách mua sắm tùy hứng</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>Shoppers love promotional gifts, so the shop added small freebies to orders.</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>Khách mua hàng rất thích quà tặng, nên cửa hàng tặng thêm quà nhỏ.</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>google/en-US-Neural2-F</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Part 2</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>B1 (Compound Sentence)</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>14 từ</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (13-14w)</t>
+        </is>
+      </c>
+      <c r="K12" s="11" t="inlineStr">
+        <is>
+          <t>Window shoppers</t>
+        </is>
+      </c>
+      <c r="L12" s="11" t="inlineStr">
+        <is>
+          <t>Người dạo ngắm đồ</t>
+        </is>
+      </c>
+      <c r="M12" s="11" t="inlineStr">
+        <is>
+          <t>Many people only browse items by day, but buy online at night.</t>
+        </is>
+      </c>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>Nhiều người chỉ ngắm đồ ban ngày, nhưng lại đặt mua vào ban đêm.</t>
+        </is>
+      </c>
+      <c r="O12" s="9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="P12" s="11" t="inlineStr">
+        <is>
+          <t>google/en-US-Neural2-F</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Part 2</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>B1 (Compound Sentence)</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>14 từ</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (13-14w)</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Integrated shopping platform</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>Nền tảng mua sắm tích hợp</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>The shopping application integrates live video, helping buyers interact very easily.</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>Ứng dụng mua sắm tích hợp video giúp người mua tương tác dễ dàng.</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>google/en-US-Neural2-F</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Part 2</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>B1 (Compound Sentence)</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>16 từ</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (15-16w)</t>
+        </is>
+      </c>
+      <c r="K14" s="11" t="inlineStr">
+        <is>
+          <t>Wholesale distributor</t>
+        </is>
+      </c>
+      <c r="L14" s="11" t="inlineStr">
+        <is>
+          <t>Nhà phân phối bán sỉ</t>
+        </is>
+      </c>
+      <c r="M14" s="11" t="inlineStr">
+        <is>
+          <t>The wholesale distributor prioritizes high volume, yet they still maintain very competitive pricing.</t>
+        </is>
+      </c>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>Nhà phân phối bán sỉ ưu tiên số lượng, nhưng vẫn giữ giá rất cạnh tranh.</t>
+        </is>
+      </c>
+      <c r="O14" s="9" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="P14" s="11" t="inlineStr">
+        <is>
+          <t>google/vi-VN-Neural2-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Part 2</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>B1 (Compound Sentence)</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>16 từ</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (15-16w)</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>Interactive live session</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>Tương tác trực tuyến đa kênh</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>The interactive live stream was crowded, and the shop completely sold out of everything.</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>Buổi tương tác trực tuyến rất đông, và cửa hàng đã bán sạch hết mọi thứ.</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>google/vi-VN-Neural2-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Part 2</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>B1 (Compound Sentence)</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>16 từ</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (15-16w)</t>
+        </is>
+      </c>
+      <c r="K16" s="11" t="inlineStr">
+        <is>
+          <t>Flash discount notification</t>
+        </is>
+      </c>
+      <c r="L16" s="11" t="inlineStr">
+        <is>
+          <t>Thông báo giảm giá sốc</t>
+        </is>
+      </c>
+      <c r="M16" s="11" t="inlineStr">
+        <is>
+          <t>The system just sent discount notifications, so shoppers immediately opened the app.</t>
+        </is>
+      </c>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>Hệ thống vừa gửi thông báo giảm giá, do đó người mua lập tức mở app.</t>
+        </is>
+      </c>
+      <c r="O16" s="9" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="P16" s="11" t="inlineStr">
+        <is>
+          <t>google/vi-VN-Neural2-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Part 3</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>B2 (Complex Sentence)</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>18 từ</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (17-18w)</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>E-commerce shopping fever</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>Cơn sốt mua sắm thương mại điện tử</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>Because retail brands rolled out massive promotions, order volume skyrocketed to record highs.</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>Bởi vì các nhãn hàng tung ra nhiều khuyến mãi, lượng đơn hàng đã tăng vọt kỷ lục.</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>google/vi-VN-Neural2-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B18" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Part 3</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>B2 (Complex Sentence)</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>18 từ</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (17-18w)</t>
+        </is>
+      </c>
+      <c r="K18" s="11" t="inlineStr">
+        <is>
+          <t>Payment data security</t>
+        </is>
+      </c>
+      <c r="L18" s="11" t="inlineStr">
+        <is>
+          <t>Bảo mật dữ liệu thanh toán</t>
+        </is>
+      </c>
+      <c r="M18" s="11" t="inlineStr">
+        <is>
+          <t>If platforms fail to secure customer data, they will lose the trust of modern consumers.</t>
+        </is>
+      </c>
+      <c r="N18" s="11" t="inlineStr">
+        <is>
+          <t>Nếu sàn không bảo mật dữ liệu khách hàng, họ sẽ mất niềm tin từ người tiêu dùng.</t>
+        </is>
+      </c>
+      <c r="O18" s="9" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="P18" s="11" t="inlineStr">
+        <is>
+          <t>google/vi-VN-Neural2-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Part 3</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>B2 (Complex Sentence)</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>18 từ</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (17-18w)</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>Customer journey optimization</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>Tối ưu hóa hành trình khách hàng</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>By recommending items matching buyer preferences, merchants can raise average order values.</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>Bằng cách gợi ý sản phẩm hợp sở thích, người bán có thể nâng cao giá trị đơn.</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>google/vi-VN-Neural2-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Part 3</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>B2 (Complex Sentence)</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G20" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>20 từ</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (19-20w)</t>
+        </is>
+      </c>
+      <c r="K20" s="11" t="inlineStr">
+        <is>
+          <t>Affiliate marketing strategy</t>
+        </is>
+      </c>
+      <c r="L20" s="11" t="inlineStr">
+        <is>
+          <t>Chiến lược tiếp thị liên kết</t>
+        </is>
+      </c>
+      <c r="M20" s="11" t="inlineStr">
+        <is>
+          <t>Although market competition is fierce, affiliate marketing remains a powerful lever for sales growth.</t>
+        </is>
+      </c>
+      <c r="N20" s="11" t="inlineStr">
+        <is>
+          <t>Dù thị trường cạnh tranh gay gắt, tiếp thị liên kết vẫn là đòn bẩy tăng trưởng doanh số mạnh.</t>
+        </is>
+      </c>
+      <c r="O20" s="9" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="P20" s="11" t="inlineStr">
+        <is>
+          <t>google/vi-VN-Neural2-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Part 3</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>B2 (Complex Sentence)</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>20 từ</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (19-20w)</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>Reputation management</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>Xử lý phản hồi tiêu cực</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>When buyers leave negative feedback, staff must quickly resolve issues to protect brand reputation.</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>Khi khách để lại đánh giá tiêu cực, nhân viên cần nhanh chóng giải quyết để bảo vệ uy tín.</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>google/vi-VN-Neural2-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B22" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Part 3</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>B2 (Complex Sentence)</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>20 từ</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (19-20w)</t>
+        </is>
+      </c>
+      <c r="K22" s="11" t="inlineStr">
+        <is>
+          <t>Personalized shopping experience</t>
+        </is>
+      </c>
+      <c r="L22" s="11" t="inlineStr">
+        <is>
+          <t>Cá nhân hóa trải nghiệm mua sắm</t>
+        </is>
+      </c>
+      <c r="M22" s="11" t="inlineStr">
+        <is>
+          <t>Employing smart personalization for shopping carts not only delights consumers, but also saves advertising budget.</t>
+        </is>
+      </c>
+      <c r="N22" s="11" t="inlineStr">
+        <is>
+          <t>Áp dụng công nghệ cá nhân hóa giỏ hàng không chỉ làm khách hài lòng, mà còn tiết kiệm tiền.</t>
+        </is>
+      </c>
+      <c r="O22" s="9" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="P22" s="11" t="inlineStr">
+        <is>
+          <t>google/vi-VN-Neural2-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Part 3</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>C1 (Advanced Sustained Fluency)</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>22 từ</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (21-22w (max))</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>Seamless payment ecosystem</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>Hệ sinh thái thanh toán tích hợp</t>
+        </is>
+      </c>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>By establishing convenient payments alongside instant delivery, online platforms have reshaped consumer shopping habits.</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>Nhờ hệ thống thanh toán tiện lợi cùng giao hàng hỏa tốc, các sàn đã thay đổi thói quen người mua sắm.</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>google/en-US-Neural2-F</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>Part 3</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>C1 (Advanced Sustained Fluency)</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G24" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>21 từ</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (21-22w (max))</t>
+        </is>
+      </c>
+      <c r="K24" s="11" t="inlineStr">
+        <is>
+          <t>Profit margin preservation</t>
+        </is>
+      </c>
+      <c r="L24" s="11" t="inlineStr">
+        <is>
+          <t>Bảo toàn biên lợi nhuận</t>
+        </is>
+      </c>
+      <c r="M24" s="11" t="inlineStr">
+        <is>
+          <t>Although discount waves attract large crowds, smart enterprises always focus on preserving their net profit margins.</t>
+        </is>
+      </c>
+      <c r="N24" s="11" t="inlineStr">
+        <is>
+          <t>Dù các đợt giảm giá mang lại lượng khách lớn, doanh nghiệp giỏi luôn chú trọng bảo toàn biên lợi nhuận.</t>
+        </is>
+      </c>
+      <c r="O24" s="9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="P24" s="11" t="inlineStr">
+        <is>
+          <t>google/en-US-Neural2-F</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Part 3</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>C1 (Advanced Sustained Fluency)</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>21 từ</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>✓ Đạt (21-22w (max))</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>Sustainable omnichannel retailing</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>Bán lẻ đa kênh bền vững</t>
+        </is>
+      </c>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>In the digital era, combining physical stores with online platforms helps retail brands grow sustainably long term.</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="inlineStr">
+        <is>
+          <t>Trong thời đại số, kết hợp cửa hàng và sàn trực tuyến giúp thương hiệu phát triển bền vững dài lâu.</t>
+        </is>
+      </c>
+      <c r="O25" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>google/en-US-Neural2-F</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2200,12 +4039,12 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="36" customWidth="1" min="9" max="9"/>
-    <col width="37" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="10" max="10"/>
     <col width="65" customWidth="1" min="11" max="11"/>
     <col width="65" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
@@ -2215,85 +4054,85 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>G02-21Q-Ecommerce-2 — G02-21Q-Ecommerce: E-commerce Market Dynamics &amp; Shopping Reflex (Focus 12V)</t>
+          <t>R01-21Q-Ecommerce-56V-1 — R01-21Q-Ecommerce: E-commerce Market Dynamics &amp; Consumer Reflexes (Awareness 56V)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fluent Complete Sentences (TL = 1.0) • Target CPD 12V • Per-Session TTS Audio</t>
+          <t>Multi-Word Cognitive Collocations (Zero Single Words) • SSML 650ms Breaks • Target CPD 56V</t>
         </is>
       </c>
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Session</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>Global #</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>Part</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>Level</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Hint Count</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
         <is>
           <t>CVR (Ω)</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>CCI (A)</t>
         </is>
       </c>
-      <c r="H4" s="12" t="inlineStr">
+      <c r="H4" s="15" t="inlineStr">
         <is>
           <t>CPD (V)</t>
         </is>
       </c>
-      <c r="I4" s="12" t="inlineStr">
-        <is>
-          <t>Term (EN)</t>
-        </is>
-      </c>
-      <c r="J4" s="12" t="inlineStr">
-        <is>
-          <t>Term (VI)</t>
-        </is>
-      </c>
-      <c r="K4" s="12" t="inlineStr">
-        <is>
-          <t>Complete Sentence (EN)</t>
-        </is>
-      </c>
-      <c r="L4" s="12" t="inlineStr">
-        <is>
-          <t>Complete Sentence (VI)</t>
-        </is>
-      </c>
-      <c r="M4" s="12" t="inlineStr">
+      <c r="I4" s="15" t="inlineStr">
+        <is>
+          <t>Collocations Constraint</t>
+        </is>
+      </c>
+      <c r="J4" s="15" t="inlineStr">
+        <is>
+          <t>Hints Sequence (EN)</t>
+        </is>
+      </c>
+      <c r="K4" s="15" t="inlineStr">
+        <is>
+          <t>Hints Sequence (VI)</t>
+        </is>
+      </c>
+      <c r="L4" s="15" t="inlineStr">
+        <is>
+          <t>Spoken SSML Script (650ms Break)</t>
+        </is>
+      </c>
+      <c r="M4" s="15" t="inlineStr">
         <is>
           <t>Audio Lang</t>
         </is>
       </c>
-      <c r="N4" s="12" t="inlineStr">
+      <c r="N4" s="15" t="inlineStr">
         <is>
           <t>Voice Model</t>
         </is>
@@ -2314,48 +4153,48 @@
           <t>Part 1</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>A2 (Simple Sentence)</t>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>2 hints</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>Impulsive shopper</t>
+        <v>55.2</v>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>Người tiêu dùng tùy hứng</t>
+          <t>e-commerce industry / fiercely competitive</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>An impulsive shopper often loves to buy on impulse during holiday sales.</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>Người tiêu dùng tùy hứng thường thích chốt đơn nhanh vào các dịp lễ hội.</t>
+          <t>Ngành thương mại điện tử / cạnh tranh khốc liệt</t>
+        </is>
+      </c>
+      <c r="L5" s="16" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;Ngành thương mại điện tử&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;cạnh tranh khốc liệt&lt;/s&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VI</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr">
         <is>
-          <t>google/en-US-Neural2-F</t>
+          <t>google/vi-VN-Neural2-A</t>
         </is>
       </c>
     </row>
@@ -2374,48 +4213,48 @@
           <t>Part 1</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>A2 (Simple Sentence)</t>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>2 hints</t>
         </is>
       </c>
       <c r="F6" s="9" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>Vibrant marketplace</t>
+        <v>55.2</v>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>Thị trường sôi động</t>
+          <t>midnight deal hunting / stay up late</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>This vibrant marketplace continues to grow rapidly with thousands of new sellers.</t>
-        </is>
-      </c>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>Thị trường sôi động này tiếp tục tăng trưởng nóng với hàng ngàn người bán mới.</t>
+          <t>Săn sale nửa đêm / thức trắng đêm</t>
+        </is>
+      </c>
+      <c r="L6" s="17" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;Săn sale nửa đêm&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;thức trắng đêm&lt;/s&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VI</t>
         </is>
       </c>
       <c r="N6" s="11" t="inlineStr">
         <is>
-          <t>google/en-US-Neural2-F</t>
+          <t>google/vi-VN-Neural2-A</t>
         </is>
       </c>
     </row>
@@ -2434,48 +4273,48 @@
           <t>Part 1</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>A2 (Simple Sentence)</t>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>2 hints</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>Secure checkout process</t>
+        <v>55.2</v>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>Quy trình thanh toán an toàn</t>
+          <t>digital wallet / linked to bank</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>A simple and secure checkout process makes online shopping very pleasant.</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>Quy trình thanh toán an toàn và đơn giản khiến việc mua hàng online rất dễ chịu.</t>
+          <t>Ví điện tử / liên kết ngân hàng</t>
+        </is>
+      </c>
+      <c r="L7" s="16" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;Ví điện tử&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;liên kết ngân hàng&lt;/s&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VI</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
         <is>
-          <t>google/en-US-Neural2-F</t>
+          <t>google/vi-VN-Neural2-A</t>
         </is>
       </c>
     </row>
@@ -2494,48 +4333,48 @@
           <t>Part 1</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>A2 (Simple Sentence)</t>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>3 hints</t>
         </is>
       </c>
       <c r="F8" s="9" t="n">
-        <v>2</v>
+        <v>7.6</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>Track package in real time</t>
+        <v>53.2</v>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>Theo dõi đơn hàng thời gian thực</t>
+          <t>e-commerce landscape / however now / saturates quickly</t>
         </is>
       </c>
       <c r="K8" s="11" t="inlineStr">
         <is>
-          <t>Customers can easily track their package delivery in real time on mobile.</t>
-        </is>
-      </c>
-      <c r="L8" s="11" t="inlineStr">
-        <is>
-          <t>Khách hàng có thể dễ dàng theo dõi hành trình bưu kiện theo thời gian thực trên điện thoại.</t>
+          <t>Thị trường thương mại điện tử / tuy nhiên vậy / bão hòa nhanh</t>
+        </is>
+      </c>
+      <c r="L8" s="17" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;Thị trường thương mại điện tử&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;tuy nhiên vậy&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;bão hòa nhanh&lt;/s&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="M8" s="9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VI</t>
         </is>
       </c>
       <c r="N8" s="11" t="inlineStr">
         <is>
-          <t>google/en-US-Neural2-F</t>
+          <t>google/vi-VN-Neural2-A</t>
         </is>
       </c>
     </row>
@@ -2554,48 +4393,48 @@
           <t>Part 1</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>A2 (Simple Sentence)</t>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>3 hints</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>2</v>
+        <v>7.6</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>Genuine product reviews</t>
+        <v>53.2</v>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>Đánh giá sản phẩm uy tín</t>
+          <t>flash sale drive / before that / hyped up</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>Reading genuine product reviews helps me choose trustworthy shops with five stars.</t>
-        </is>
-      </c>
-      <c r="L9" s="7" t="inlineStr">
-        <is>
-          <t>Đọc đánh giá sản phẩm thực tế giúp tôi chọn được các cửa hàng năm sao uy tín.</t>
+          <t>Chiến dịch săn sale / trước đó trước / quảng bá rầm rộ</t>
+        </is>
+      </c>
+      <c r="L9" s="16" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;Chiến dịch săn sale&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;trước đó trước&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;quảng bá rầm rộ&lt;/s&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VI</t>
         </is>
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>google/en-US-Neural2-F</t>
+          <t>google/vi-VN-Neural2-A</t>
         </is>
       </c>
     </row>
@@ -2614,48 +4453,48 @@
           <t>Part 1</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>A2 (Simple Sentence)</t>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>3 hints</t>
         </is>
       </c>
       <c r="F10" s="9" t="n">
-        <v>2</v>
+        <v>7.6</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="I10" s="11" t="inlineStr">
-        <is>
-          <t>Discount voucher code</t>
+        <v>53.2</v>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>Mã giảm giá ưu đãi</t>
+          <t>e-wallet checkout / meanwhile now / get cashback</t>
         </is>
       </c>
       <c r="K10" s="11" t="inlineStr">
         <is>
-          <t>Do not forget to apply your discount voucher before making final payment.</t>
-        </is>
-      </c>
-      <c r="L10" s="11" t="inlineStr">
-        <is>
-          <t>Đừng quên nhập mã giảm giá ưu đãi trước khi tiến hành thanh toán cuối cùng.</t>
+          <t>Thanh toán ví điện tử / đồng thời cùng lúc / nhận mã hoàn tiền</t>
+        </is>
+      </c>
+      <c r="L10" s="17" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;Thanh toán ví điện tử&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;đồng thời cùng lúc&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;nhận mã hoàn tiền&lt;/s&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VI</t>
         </is>
       </c>
       <c r="N10" s="11" t="inlineStr">
         <is>
-          <t>google/en-US-Neural2-F</t>
+          <t>google/vi-VN-Neural2-A</t>
         </is>
       </c>
     </row>
@@ -2674,48 +4513,48 @@
           <t>Part 2</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>B1 (Compound Sentence)</t>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>4 hints</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>3</v>
+        <v>10.6</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>Impulsive shoppers</t>
+        <v>53</v>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>Khách mua sắm tùy hứng</t>
+          <t>e-commerce arena / while now / lucrative pie / everyone wants slice</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>Impulsive shoppers love freebies, so we added exclusive gifts to each order.</t>
-        </is>
-      </c>
-      <c r="L11" s="7" t="inlineStr">
-        <is>
-          <t>Khách mua hàng rất thích quà tặng kèm, vì vậy chúng tôi đã thêm ưu đãi vào đơn.</t>
+          <t>Ngành thương mại điện tử / trong khi đó / miếng bánh màu mỡ / ai cũng muốn chia phần</t>
+        </is>
+      </c>
+      <c r="L11" s="16" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;Ngành thương mại điện tử&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;trong khi đó&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;miếng bánh màu mỡ&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;ai cũng muốn chia phần&lt;/s&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VI</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>google/en-US-Neural2-F</t>
+          <t>google/vi-VN-Neural2-A</t>
         </is>
       </c>
     </row>
@@ -2734,48 +4573,48 @@
           <t>Part 2</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>B1 (Compound Sentence)</t>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>4 hints</t>
         </is>
       </c>
       <c r="F12" s="9" t="n">
-        <v>3</v>
+        <v>10.6</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>Window shoppers</t>
+        <v>53</v>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>Người dạo ngắm đồ</t>
+          <t>When now / otherwise now / shopping frenzy / crash servers</t>
         </is>
       </c>
       <c r="K12" s="11" t="inlineStr">
         <is>
-          <t>Many people browse items in store windows during the day, and then they buy online at night.</t>
-        </is>
-      </c>
-      <c r="L12" s="11" t="inlineStr">
-        <is>
-          <t>Nhiều người dạo ngắm đồ trên phố ban ngày, rồi sau đó họ đặt mua trực tuyến vào ban đêm.</t>
+          <t>Bất cứ khi nào / nếu không thì / cơn bão săn sale / sẽ làm sập hệ thống</t>
+        </is>
+      </c>
+      <c r="L12" s="17" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;Bất cứ khi nào&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;nếu không thì&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;cơn bão săn sale&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;sẽ làm sập hệ thống&lt;/s&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="M12" s="9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VI</t>
         </is>
       </c>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>google/en-US-Neural2-F</t>
+          <t>google/vi-VN-Neural2-A</t>
         </is>
       </c>
     </row>
@@ -2794,48 +4633,48 @@
           <t>Part 2</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>B1 (Compound Sentence)</t>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>4 hints</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>3</v>
+        <v>10.6</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>Integrated shopping platform</t>
+        <v>53</v>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>Nền tảng mua sắm tích hợp</t>
+          <t>linked e-wallet / however now / customer magnet / boost retention</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>The modern shopping platform embeds live video, so buyers can interact directly with sellers.</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>Nền tảng mua sắm hiện nay tích hợp livestream, giúp người tiêu dùng tương tác trực tiếp với người bán.</t>
+          <t>Ví điện tử liên kết / tuy nhiên vậy / thỏi nam châm hút khách / tăng độ gắn kết</t>
+        </is>
+      </c>
+      <c r="L13" s="16" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;Ví điện tử liên kết&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;tuy nhiên vậy&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;thỏi nam châm hút khách&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;tăng độ gắn kết&lt;/s&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VI</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>google/en-US-Neural2-F</t>
+          <t>google/vi-VN-Neural2-A</t>
         </is>
       </c>
     </row>
@@ -2854,48 +4693,48 @@
           <t>Part 2</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>B1 (Compound Sentence)</t>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>2 hints</t>
         </is>
       </c>
       <c r="F14" s="9" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="I14" s="11" t="inlineStr">
-        <is>
-          <t>Wholesale distributor</t>
+        <v>58</v>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>Nhà phân phối bán sỉ</t>
+          <t>cash-burning game / financially drained</t>
         </is>
       </c>
       <c r="K14" s="11" t="inlineStr">
         <is>
-          <t>The wholesale distributor prioritizes high volume, yet they still maintain very competitive rates.</t>
-        </is>
-      </c>
-      <c r="L14" s="11" t="inlineStr">
-        <is>
-          <t>Nhà phân phối bán sỉ luôn ưu tiên số lượng lớn, nhưng họ vẫn duy trì mức giá rất cạnh tranh.</t>
+          <t>Trò chơi đốt tiền / kiệt quệ tài chính</t>
+        </is>
+      </c>
+      <c r="L14" s="17" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;cash-burning game&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;financially drained&lt;/s&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="M14" s="9" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>google/vi-VN-Neural2-A</t>
+          <t>google/en-US-Neural2-F</t>
         </is>
       </c>
     </row>
@@ -2914,48 +4753,48 @@
           <t>Part 2</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>B1 (Compound Sentence)</t>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>2 hints</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>Interactive live session</t>
+        <v>58</v>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>Tương tác trực tuyến đa kênh</t>
+          <t>competitive pricing / draw customers</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>The interactive live session attracted thousands of viewers, and the shop sold out within half an hour.</t>
-        </is>
-      </c>
-      <c r="L15" s="7" t="inlineStr">
-        <is>
-          <t>Buổi tương tác trực tuyến thu hút hàng ngàn lượt xem, và cửa hàng đã bán hết sạch hàng chỉ sau nửa giờ.</t>
+          <t>Mức giá cạnh tranh / thu hút khách mua</t>
+        </is>
+      </c>
+      <c r="L15" s="16" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;competitive pricing&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;draw customers&lt;/s&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>google/vi-VN-Neural2-A</t>
+          <t>google/en-US-Neural2-F</t>
         </is>
       </c>
     </row>
@@ -2974,48 +4813,48 @@
           <t>Part 2</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>B1 (Compound Sentence)</t>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>2 hints</t>
         </is>
       </c>
       <c r="F16" s="9" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="I16" s="11" t="inlineStr">
-        <is>
-          <t>Flash discount notification</t>
+        <v>58</v>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>Thông báo giảm giá sốc</t>
+          <t>impulsive spender / buy on impulse</t>
         </is>
       </c>
       <c r="K16" s="11" t="inlineStr">
         <is>
-          <t>The mobile app just pushed a flash discount notification, so buyers immediately checked their phones.</t>
-        </is>
-      </c>
-      <c r="L16" s="11" t="inlineStr">
-        <is>
-          <t>Ứng dụng vừa gửi thông báo giảm giá sốc, do đó người mua ngay lập tức mở điện thoại để săn đồ.</t>
+          <t>Người tiêu dùng tùy hứng / chốt đơn nhanh</t>
+        </is>
+      </c>
+      <c r="L16" s="17" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;impulsive spender&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;buy on impulse&lt;/s&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="M16" s="9" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>google/vi-VN-Neural2-A</t>
+          <t>google/en-US-Neural2-F</t>
         </is>
       </c>
     </row>
@@ -3034,48 +4873,48 @@
           <t>Part 3</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>B2 (Complex Sentence)</t>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>3 hints</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>E-commerce shopping fever</t>
+        <v>55.8</v>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>Cơn sốt mua sắm thương mại điện tử</t>
+          <t>cash burning tactics / therefore now / unsustainable now</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>Because top brands released numerous promotional codes on the shopping festival, order volume skyrocketed to record highs.</t>
-        </is>
-      </c>
-      <c r="L17" s="7" t="inlineStr">
-        <is>
-          <t>Bởi vì các thương hiệu tung ra hàng loạt mã khuyến mãi vào ngày hội mua sắm, lượng đơn hàng đã tăng vọt kỷ lục.</t>
+          <t>Chiêu trò đốt tiền / do đó cho nên / không bền lâu dài</t>
+        </is>
+      </c>
+      <c r="L17" s="16" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;cash burning tactics&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;therefore now&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;unsustainable now&lt;/s&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>google/vi-VN-Neural2-A</t>
+          <t>google/en-US-Neural2-F</t>
         </is>
       </c>
     </row>
@@ -3094,48 +4933,48 @@
           <t>Part 3</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>B2 (Complex Sentence)</t>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>3 hints</t>
         </is>
       </c>
       <c r="F18" s="9" t="n">
-        <v>4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="I18" s="11" t="inlineStr">
-        <is>
-          <t>Payment data security</t>
+        <v>55.8</v>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>Bảo mật dữ liệu thanh toán</t>
+          <t>competitive pricing / otherwise now / lose market share</t>
         </is>
       </c>
       <c r="K18" s="11" t="inlineStr">
         <is>
-          <t>If platforms fail to invest in rigorous payment data security, they will completely lose the hard-earned trust of their users.</t>
-        </is>
-      </c>
-      <c r="L18" s="11" t="inlineStr">
-        <is>
-          <t>Nếu nền tảng không đầu tư bảo mật thông tin thanh toán nghiêm ngặt, họ sẽ đánh mất hoàn toàn niềm tin từ cộng đồng người dùng.</t>
+          <t>Chiến lược giá cạnh tranh / nếu không thì / mất thị phần</t>
+        </is>
+      </c>
+      <c r="L18" s="17" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;competitive pricing&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;otherwise now&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;lose market share&lt;/s&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="M18" s="9" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>google/vi-VN-Neural2-A</t>
+          <t>google/en-US-Neural2-F</t>
         </is>
       </c>
     </row>
@@ -3154,48 +4993,48 @@
           <t>Part 3</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>B2 (Complex Sentence)</t>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>3 hints</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>Customer journey optimization</t>
+        <v>55.8</v>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>Tối ưu hóa hành trình khách hàng</t>
+          <t>impulsive shoppers / in addition / love freebies</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>By analyzing browsing habits and recommending relevant products, retailers can noticeably increase their average order value.</t>
-        </is>
-      </c>
-      <c r="L19" s="7" t="inlineStr">
-        <is>
-          <t>Bằng cách phân tích hành vi duyệt web và đề xuất sản phẩm phù hợp, cửa hàng có thể nâng cao đáng kể giá trị trung bình trên mỗi đơn.</t>
+          <t>Khách mua sắm tùy hứng / hơn thế nữa / thích quà tặng kèm</t>
+        </is>
+      </c>
+      <c r="L19" s="16" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;impulsive shoppers&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;in addition&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;love freebies&lt;/s&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>google/vi-VN-Neural2-A</t>
+          <t>google/en-US-Neural2-F</t>
         </is>
       </c>
     </row>
@@ -3214,48 +5053,48 @@
           <t>Part 3</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>B2 (Complex Sentence)</t>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>4 hints</t>
         </is>
       </c>
       <c r="F20" s="9" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="G20" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G20" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="H20" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="I20" s="11" t="inlineStr">
-        <is>
-          <t>Affiliate marketing strategy</t>
+        <v>51.6</v>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J20" s="11" t="inlineStr">
         <is>
-          <t>Chiến lược tiếp thị liên kết</t>
+          <t>cash-burning war / therefore now / bottomless pit / swallow capital</t>
         </is>
       </c>
       <c r="K20" s="11" t="inlineStr">
         <is>
-          <t>Although market competition is exceptionally fierce, a smart affiliate marketing strategy created immense leverage for rapid revenue growth.</t>
-        </is>
-      </c>
-      <c r="L20" s="11" t="inlineStr">
-        <is>
-          <t>Mặc dù thị trường cạnh tranh vô cùng gay gắt, chiến lược tiếp thị liên kết thông minh đã tạo ra đòn bẩy tăng trưởng doanh số vượt bậc.</t>
+          <t>Trò chơi đốt tiền / do đó cho nên / hố sâu không đáy / nuốt trọn nguồn vốn</t>
+        </is>
+      </c>
+      <c r="L20" s="17" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;cash-burning war&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;therefore now&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;bottomless pit&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;swallow capital&lt;/s&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="M20" s="9" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="N20" s="11" t="inlineStr">
         <is>
-          <t>google/vi-VN-Neural2-A</t>
+          <t>google/en-US-Neural2-F</t>
         </is>
       </c>
     </row>
@@ -3274,48 +5113,48 @@
           <t>Part 3</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>B2 (Complex Sentence)</t>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>4 hints</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="G21" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="G21" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="H21" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>Reputation management</t>
+        <v>51.6</v>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>Xử lý phản hồi tiêu cực</t>
+          <t>aggressive price cuts / although now / double-edged blade / erode profit margins</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>When negative one-star reviews arise from dissatisfied buyers, customer support must proactively listen and resolve issues to protect brand reputation.</t>
-        </is>
-      </c>
-      <c r="L21" s="7" t="inlineStr">
-        <is>
-          <t>Khi phát sinh các đánh giá một sao từ khách hàng, bộ phận chăm sóc phải chủ động lắng nghe và giải quyết thỏa đáng để bảo vệ danh tiếng.</t>
+          <t>Giá cả cạnh tranh / mặc dù vậy / con dao hai lưỡi / bào mòn lợi nhuận</t>
+        </is>
+      </c>
+      <c r="L21" s="16" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;aggressive price cuts&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;although now&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;double-edged blade&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;erode profit margins&lt;/s&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>google/vi-VN-Neural2-A</t>
+          <t>google/en-US-Neural2-F</t>
         </is>
       </c>
     </row>
@@ -3334,48 +5173,48 @@
           <t>Part 3</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>B2 (Complex Sentence)</t>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>4 hints</t>
         </is>
       </c>
       <c r="F22" s="9" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="G22" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G22" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="H22" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="I22" s="11" t="inlineStr">
-        <is>
-          <t>Personalized shopping experience</t>
+        <v>51.6</v>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J22" s="11" t="inlineStr">
         <is>
-          <t>Cá nhân hóa trải nghiệm mua sắm</t>
+          <t>Why now / moreover now / shopaholic instinct / overspend wildly</t>
         </is>
       </c>
       <c r="K22" s="11" t="inlineStr">
         <is>
-          <t>Employing artificial intelligence to personalize shopping carts not only delights consumers, but also substantially optimizes digital marketing expenditures.</t>
-        </is>
-      </c>
-      <c r="L22" s="11" t="inlineStr">
-        <is>
-          <t>Việc áp dụng công nghệ trí tuệ nhân tạo để cá nhân hóa giỏ hàng không những làm hài lòng khách mua, mà còn tối ưu hóa chi phí tiếp thị.</t>
+          <t>Lý do vì sao / hơn thế nữa / con nghiện mua sắm / vung tay quá trán</t>
+        </is>
+      </c>
+      <c r="L22" s="17" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;Why now&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;moreover now&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;shopaholic instinct&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;overspend wildly&lt;/s&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="M22" s="9" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="N22" s="11" t="inlineStr">
         <is>
-          <t>google/vi-VN-Neural2-A</t>
+          <t>google/en-US-Neural2-F</t>
         </is>
       </c>
     </row>
@@ -3394,38 +5233,38 @@
           <t>Part 3</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>C1 (Advanced Sustained Fluency)</t>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>4 hints</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>6</v>
+        <v>13.8</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>Seamless payment ecosystem</t>
+        <v>55.2</v>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>Hệ sinh thái thanh toán tích hợp</t>
+          <t>window shopping stroll / then now / sweet bait / trigger instant buy</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>By engineering a seamless digital payment ecosystem paired with ultra-fast logistics, leading e-commerce platforms have fundamentally reshaped modern consumer spending habits.</t>
-        </is>
-      </c>
-      <c r="L23" s="7" t="inlineStr">
-        <is>
-          <t>Nhờ xây dựng một hệ sinh thái thanh toán số liền mạch kết hợp giao hàng siêu tốc, các nền tảng bán lẻ hàng đầu đã tái định hình toàn bộ thói quen chi tiêu của người tiêu dùng.</t>
+          <t>Đi lượn lờ ngắm đồ / sau đó liền / mồi câu hấp dẫn / khiến chốt đơn ngay</t>
+        </is>
+      </c>
+      <c r="L23" s="16" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;window shopping stroll&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;then now&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;sweet bait&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;trigger instant buy&lt;/s&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
@@ -3454,38 +5293,38 @@
           <t>Part 3</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
-        <is>
-          <t>C1 (Advanced Sustained Fluency)</t>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>4 hints</t>
         </is>
       </c>
       <c r="F24" s="9" t="n">
-        <v>6</v>
+        <v>13.8</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="I24" s="11" t="inlineStr">
-        <is>
-          <t>Profit margin preservation</t>
+        <v>55.2</v>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr">
         <is>
-          <t>Bảo toàn biên lợi nhuận</t>
+          <t>stuffed cart / instead of that / FOMO fever / rush to checkout</t>
         </is>
       </c>
       <c r="K24" s="11" t="inlineStr">
         <is>
-          <t>Although aggressive promotional price cuts generate massive initial traffic surges, top enterprise merchants always prioritize sustainable cash flow and net margin preservation.</t>
-        </is>
-      </c>
-      <c r="L24" s="11" t="inlineStr">
-        <is>
-          <t>Mặc dù các đợt giảm giá kích cầu chớp nhoáng có thể mang lại lượng truy cập khổng lồ, những doanh nghiệp xuất sắc luôn ưu tiên bảo toàn biên lợi nhuận ròng và dòng tiền thực tế.</t>
+          <t>Giỏ hàng đầy ắp / thay vào đó / nỗi sợ bỏ lỡ / thúc giục thanh toán</t>
+        </is>
+      </c>
+      <c r="L24" s="17" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;stuffed cart&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;instead of that&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;FOMO fever&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;rush to checkout&lt;/s&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="M24" s="9" t="inlineStr">
@@ -3514,1277 +5353,6 @@
           <t>Part 3</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>C1 (Advanced Sustained Fluency)</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>Sustainable omnichannel retailing</t>
-        </is>
-      </c>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>Chiến lược bán lẻ đa kênh bền vững</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="inlineStr">
-        <is>
-          <t>In an era of ubiquitous digital commerce, establishing seamless synergy between physical flagship showrooms and online retail touchpoints unlocks unprecedented customer lifetime value.</t>
-        </is>
-      </c>
-      <c r="L25" s="7" t="inlineStr">
-        <is>
-          <t>Trong kỷ nguyên số hóa toàn diện, sự cộng hưởng nhịp nhàng giữa cửa hàng trải nghiệm thực tế và nền tảng mua sắm trực tuyến chính là chìa khóa mở ra tiềm năng tăng trưởng vô tận.</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="N25" s="7" t="inlineStr">
-        <is>
-          <t>google/en-US-Neural2-F</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
-  <cols>
-    <col width="65" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="65" customWidth="1" min="9" max="9"/>
-    <col width="65" customWidth="1" min="10" max="10"/>
-    <col width="65" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="25" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>R01-21Q-Ecommerce-56V-1 — R01-21Q-Ecommerce: E-commerce Market Dynamics &amp; Consumer Reflexes (Awareness 56V)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Cognitive Traps &amp; 650ms SSML Breaks • Hint Progression [2,3,4,2,3,4,4] • Target CPD 56V</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>Session</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>Global #</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>Part</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>Hint Count</t>
-        </is>
-      </c>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>CVR (Ω)</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>CCI (A)</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>CPD (V)</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>Hints Sequence (EN)</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
-        <is>
-          <t>Hints Sequence (VI)</t>
-        </is>
-      </c>
-      <c r="K4" s="13" t="inlineStr">
-        <is>
-          <t>Spoken SSML Script (650ms Break)</t>
-        </is>
-      </c>
-      <c r="L4" s="13" t="inlineStr">
-        <is>
-          <t>Audio Lang</t>
-        </is>
-      </c>
-      <c r="M4" s="13" t="inlineStr">
-        <is>
-          <t>Voice Model</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Part 1</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>2 hints</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>e-commerce industry / fiercely competitive</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>Ngành thương mại điện tử / cạnh tranh khốc liệt</t>
-        </is>
-      </c>
-      <c r="K5" s="14" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;Ngành thương mại điện tử&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;cạnh tranh khốc liệt&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>VI</t>
-        </is>
-      </c>
-      <c r="M5" s="7" t="inlineStr">
-        <is>
-          <t>google/vi-VN-Neural2-A</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>Part 1</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>2 hints</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="H6" s="9" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>midnight deal hunting / stay up late</t>
-        </is>
-      </c>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>Săn sale nửa đêm / thức trắng</t>
-        </is>
-      </c>
-      <c r="K6" s="15" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;Săn sale nửa đêm&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;thức trắng&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L6" s="9" t="inlineStr">
-        <is>
-          <t>VI</t>
-        </is>
-      </c>
-      <c r="M6" s="11" t="inlineStr">
-        <is>
-          <t>google/vi-VN-Neural2-A</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Part 1</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>2 hints</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>digital wallet / linked to bank</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>Ví điện tử / liên kết ngân hàng</t>
-        </is>
-      </c>
-      <c r="K7" s="14" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;Ví điện tử&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;liên kết ngân hàng&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>VI</t>
-        </is>
-      </c>
-      <c r="M7" s="7" t="inlineStr">
-        <is>
-          <t>google/vi-VN-Neural2-A</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>Part 1</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>3 hints</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="G8" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H8" s="9" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>e-commerce landscape / however / saturates quickly</t>
-        </is>
-      </c>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>Thị trường thương mại điện tử / tuy nhiên / bão hòa nhanh</t>
-        </is>
-      </c>
-      <c r="K8" s="15" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;Thị trường thương mại điện tử&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;tuy nhiên&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;bão hòa nhanh&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L8" s="9" t="inlineStr">
-        <is>
-          <t>VI</t>
-        </is>
-      </c>
-      <c r="M8" s="11" t="inlineStr">
-        <is>
-          <t>google/vi-VN-Neural2-A</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Part 1</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>3 hints</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>flash sale drive / before that / hyped up</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>Chiến dịch săn sale / trước đó / quảng bá rầm rộ</t>
-        </is>
-      </c>
-      <c r="K9" s="14" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;Chiến dịch săn sale&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;trước đó&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;quảng bá rầm rộ&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>VI</t>
-        </is>
-      </c>
-      <c r="M9" s="7" t="inlineStr">
-        <is>
-          <t>google/vi-VN-Neural2-A</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>Part 1</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>3 hints</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="G10" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H10" s="9" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="I10" s="11" t="inlineStr">
-        <is>
-          <t>e-wallet checkout / meanwhile / get cashback</t>
-        </is>
-      </c>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>Thanh toán ví điện tử / đồng thời / nhận mã hoàn tiền</t>
-        </is>
-      </c>
-      <c r="K10" s="15" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;Thanh toán ví điện tử&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;đồng thời&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;nhận mã hoàn tiền&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L10" s="9" t="inlineStr">
-        <is>
-          <t>VI</t>
-        </is>
-      </c>
-      <c r="M10" s="11" t="inlineStr">
-        <is>
-          <t>google/vi-VN-Neural2-A</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Part 2</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>4 hints</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>53</v>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>e-commerce arena / while / lucrative pie / everyone wants slice</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>Ngành thương mại điện tử / trong khi / miếng bánh màu mỡ / ai cũng muốn chia phần</t>
-        </is>
-      </c>
-      <c r="K11" s="14" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;Ngành thương mại điện tử&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;trong khi&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;miếng bánh màu mỡ&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;ai cũng muốn chia phần&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>VI</t>
-        </is>
-      </c>
-      <c r="M11" s="7" t="inlineStr">
-        <is>
-          <t>google/vi-VN-Neural2-A</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="B12" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>Part 2</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>4 hints</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="G12" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H12" s="9" t="n">
-        <v>53</v>
-      </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>When / otherwise / shopping frenzy / crash servers</t>
-        </is>
-      </c>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
-          <t>Khi nào / nếu không / cơn bão săn sale / sẽ làm sập hệ thống</t>
-        </is>
-      </c>
-      <c r="K12" s="15" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;Khi nào&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;nếu không&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;cơn bão săn sale&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;sẽ làm sập hệ thống&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L12" s="9" t="inlineStr">
-        <is>
-          <t>VI</t>
-        </is>
-      </c>
-      <c r="M12" s="11" t="inlineStr">
-        <is>
-          <t>google/vi-VN-Neural2-A</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Part 2</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>4 hints</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>53</v>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>linked e-wallet / however / customer magnet / boost retention</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>Ví điện tử liên kết / tuy nhiên / thỏi nam châm hút khách / tăng độ gắn kết</t>
-        </is>
-      </c>
-      <c r="K13" s="14" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;Ví điện tử liên kết&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;tuy nhiên&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;thỏi nam châm hút khách&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;tăng độ gắn kết&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>VI</t>
-        </is>
-      </c>
-      <c r="M13" s="7" t="inlineStr">
-        <is>
-          <t>google/vi-VN-Neural2-A</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="B14" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>Part 2</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>2 hints</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H14" s="9" t="n">
-        <v>58</v>
-      </c>
-      <c r="I14" s="11" t="inlineStr">
-        <is>
-          <t>cash-burning game / financially drained</t>
-        </is>
-      </c>
-      <c r="J14" s="11" t="inlineStr">
-        <is>
-          <t>Trò chơi đốt tiền / kiệt quệ tài chính</t>
-        </is>
-      </c>
-      <c r="K14" s="15" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;cash-burning game&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;financially drained&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L14" s="9" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="M14" s="11" t="inlineStr">
-        <is>
-          <t>google/en-US-Neural2-F</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>Part 2</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>2 hints</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>competitive pricing / draw customers</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>Mức giá cạnh tranh / hút khách</t>
-        </is>
-      </c>
-      <c r="K15" s="14" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;competitive pricing&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;draw customers&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="M15" s="7" t="inlineStr">
-        <is>
-          <t>google/en-US-Neural2-F</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="B16" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>Part 2</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>2 hints</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="G16" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H16" s="9" t="n">
-        <v>58</v>
-      </c>
-      <c r="I16" s="11" t="inlineStr">
-        <is>
-          <t>impulsive spender / buy on impulse</t>
-        </is>
-      </c>
-      <c r="J16" s="11" t="inlineStr">
-        <is>
-          <t>Người tiêu dùng tùy hứng / chốt đơn nhanh</t>
-        </is>
-      </c>
-      <c r="K16" s="15" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;impulsive spender&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;buy on impulse&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L16" s="9" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="M16" s="11" t="inlineStr">
-        <is>
-          <t>google/en-US-Neural2-F</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Part 3</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>3 hints</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>cash burning tactics / therefore / unsustainable</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>Chiêu trò đốt tiền / do đó / không bền lâu</t>
-        </is>
-      </c>
-      <c r="K17" s="14" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;cash burning tactics&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;therefore&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;unsustainable&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="M17" s="7" t="inlineStr">
-        <is>
-          <t>google/en-US-Neural2-F</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="B18" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>Part 3</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>3 hints</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="G18" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="H18" s="9" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="I18" s="11" t="inlineStr">
-        <is>
-          <t>competitive pricing / otherwise / lose market share</t>
-        </is>
-      </c>
-      <c r="J18" s="11" t="inlineStr">
-        <is>
-          <t>Chiến lược giá cạnh tranh / nếu không / mất thị phần</t>
-        </is>
-      </c>
-      <c r="K18" s="15" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;competitive pricing&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;otherwise&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;lose market share&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L18" s="9" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="M18" s="11" t="inlineStr">
-        <is>
-          <t>google/en-US-Neural2-F</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Part 3</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>3 hints</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>impulsive shoppers / in addition / love freebies</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>Khách mua sắm tùy hứng / hơn nữa / thích quà tặng kèm</t>
-        </is>
-      </c>
-      <c r="K19" s="14" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;impulsive shoppers&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;in addition&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;love freebies&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="M19" s="7" t="inlineStr">
-        <is>
-          <t>google/en-US-Neural2-F</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B20" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>Part 3</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>4 hints</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="G20" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H20" s="9" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="I20" s="11" t="inlineStr">
-        <is>
-          <t>cash-burning war / therefore / bottomless pit / swallow capital</t>
-        </is>
-      </c>
-      <c r="J20" s="11" t="inlineStr">
-        <is>
-          <t>Trò chơi đốt tiền / do đó / hố sâu không đáy / nuốt trọn nguồn vốn</t>
-        </is>
-      </c>
-      <c r="K20" s="15" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;cash-burning war&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;therefore&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;bottomless pit&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;swallow capital&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L20" s="9" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="M20" s="11" t="inlineStr">
-        <is>
-          <t>google/en-US-Neural2-F</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Part 3</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>4 hints</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>aggressive price cuts / although / double-edged blade / erode profit margins</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>Giá cả cạnh tranh / mặc dù / con dao hai lưỡi / bào mòn lợi nhuận</t>
-        </is>
-      </c>
-      <c r="K21" s="14" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;aggressive price cuts&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;although&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;double-edged blade&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;erode profit margins&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="M21" s="7" t="inlineStr">
-        <is>
-          <t>google/en-US-Neural2-F</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B22" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C22" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>Part 3</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>4 hints</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="G22" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H22" s="9" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="I22" s="11" t="inlineStr">
-        <is>
-          <t>Why / moreover / shopaholic instinct / overspend wildly</t>
-        </is>
-      </c>
-      <c r="J22" s="11" t="inlineStr">
-        <is>
-          <t>Vì sao / hơn nữa / con nghiện mua sắm / vung tay quá trán</t>
-        </is>
-      </c>
-      <c r="K22" s="15" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;Why&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;moreover&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;shopaholic instinct&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;overspend wildly&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L22" s="9" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="M22" s="11" t="inlineStr">
-        <is>
-          <t>google/en-US-Neural2-F</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>Part 3</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>4 hints</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>window shopping stroll / then / sweet bait / trigger instant buy</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>Đi lượn lờ ngắm đồ / sau đó / mồi câu hấp dẫn / khiến chốt đơn ngay</t>
-        </is>
-      </c>
-      <c r="K23" s="14" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;window shopping stroll&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;then&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;sweet bait&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;trigger instant buy&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="M23" s="7" t="inlineStr">
-        <is>
-          <t>google/en-US-Neural2-F</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B24" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C24" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>Part 3</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>4 hints</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="G24" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H24" s="9" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="I24" s="11" t="inlineStr">
-        <is>
-          <t>stuffed cart / instead / FOMO fever / rush to checkout</t>
-        </is>
-      </c>
-      <c r="J24" s="11" t="inlineStr">
-        <is>
-          <t>Giỏ hàng đầy ắp / thay vào đó / nỗi sợ bỏ lỡ / thúc giục thanh toán</t>
-        </is>
-      </c>
-      <c r="K24" s="15" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;stuffed cart&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;instead&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;FOMO fever&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;rush to checkout&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L24" s="9" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="M24" s="11" t="inlineStr">
-        <is>
-          <t>google/en-US-Neural2-F</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Part 3</t>
-        </is>
-      </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
           <t>4 hints</t>
@@ -4799,27 +5367,32 @@
       <c r="H25" s="5" t="n">
         <v>55.2</v>
       </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>How long / if / data leak breach / lose trust entirely</t>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>Bao lâu / nếu / rò rỉ dữ liệu / mất hết uy tín</t>
-        </is>
-      </c>
-      <c r="K25" s="14" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;How long&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;if&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;data leak breach&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;lose trust entirely&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
+          <t>How long / if now / data leak breach / lose trust entirely</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>Bao lâu / nếu không cẩn thận / rò rỉ dữ liệu / mất hết uy tín</t>
+        </is>
+      </c>
+      <c r="L25" s="16" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;How long&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;if now&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;data leak breach&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;lose trust entirely&lt;/s&gt;&lt;/speak&gt;</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="M25" s="7" t="inlineStr">
+      <c r="N25" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -4836,7 +5409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
@@ -4847,11 +5420,12 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="65" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
     <col width="65" customWidth="1" min="10" max="10"/>
     <col width="65" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="65" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4864,73 +5438,78 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Cognitive Traps &amp; 650ms SSML Breaks • Hint Progression [2,3,4,2,3,4,4] • Target CPD 56V</t>
+          <t>Multi-Word Cognitive Collocations (Zero Single Words) • SSML 650ms Breaks • Target CPD 56V</t>
         </is>
       </c>
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Session</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>Global #</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>Part</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>Hint Count</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="15" t="inlineStr">
         <is>
           <t>CVR (Ω)</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>CCI (A)</t>
         </is>
       </c>
-      <c r="H4" s="13" t="inlineStr">
+      <c r="H4" s="15" t="inlineStr">
         <is>
           <t>CPD (V)</t>
         </is>
       </c>
-      <c r="I4" s="13" t="inlineStr">
+      <c r="I4" s="15" t="inlineStr">
+        <is>
+          <t>Collocations Constraint</t>
+        </is>
+      </c>
+      <c r="J4" s="15" t="inlineStr">
         <is>
           <t>Hints Sequence (EN)</t>
         </is>
       </c>
-      <c r="J4" s="13" t="inlineStr">
+      <c r="K4" s="15" t="inlineStr">
         <is>
           <t>Hints Sequence (VI)</t>
         </is>
       </c>
-      <c r="K4" s="13" t="inlineStr">
+      <c r="L4" s="15" t="inlineStr">
         <is>
           <t>Spoken SSML Script (650ms Break)</t>
         </is>
       </c>
-      <c r="L4" s="13" t="inlineStr">
+      <c r="M4" s="15" t="inlineStr">
         <is>
           <t>Audio Lang</t>
         </is>
       </c>
-      <c r="M4" s="13" t="inlineStr">
+      <c r="N4" s="15" t="inlineStr">
         <is>
           <t>Voice Model</t>
         </is>
@@ -4965,27 +5544,32 @@
       <c r="H5" s="5" t="n">
         <v>55.2</v>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>impulsive spender / buy on impulse</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>Người tiêu dùng tùy hứng / chốt đơn nhanh</t>
         </is>
       </c>
-      <c r="K5" s="14" t="inlineStr">
+      <c r="L5" s="16" t="inlineStr">
         <is>
           <t>&lt;speak&gt;&lt;s&gt;Người tiêu dùng tùy hứng&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;chốt đơn nhanh&lt;/s&gt;&lt;/speak&gt;</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -5020,27 +5604,32 @@
       <c r="H6" s="9" t="n">
         <v>55.2</v>
       </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>window shopping / unwind</t>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>Đi lượn lờ ngó nghiêng / xả stress</t>
-        </is>
-      </c>
-      <c r="K6" s="15" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;Đi lượn lờ ngó nghiêng&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;xả stress&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L6" s="9" t="inlineStr">
+          <t>window shopping / unwind now</t>
+        </is>
+      </c>
+      <c r="K6" s="11" t="inlineStr">
+        <is>
+          <t>Đi lượn lờ ngó nghiêng / giải tỏa căng thẳng</t>
+        </is>
+      </c>
+      <c r="L6" s="17" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;Đi lượn lờ ngó nghiêng&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;giải tỏa căng thẳng&lt;/s&gt;&lt;/speak&gt;</t>
+        </is>
+      </c>
+      <c r="M6" s="9" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr">
+      <c r="N6" s="11" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -5075,27 +5664,32 @@
       <c r="H7" s="5" t="n">
         <v>55.2</v>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>vibrant marketplace / grow rapidly</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>Thị trường sôi động / tăng trưởng nóng</t>
         </is>
       </c>
-      <c r="K7" s="14" t="inlineStr">
+      <c r="L7" s="16" t="inlineStr">
         <is>
           <t>&lt;speak&gt;&lt;s&gt;Thị trường sôi động&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;tăng trưởng nóng&lt;/s&gt;&lt;/speak&gt;</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="M7" s="7" t="inlineStr">
+      <c r="N7" s="7" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -5130,27 +5724,32 @@
       <c r="H8" s="9" t="n">
         <v>53.2</v>
       </c>
-      <c r="I8" s="11" t="inlineStr">
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>impulsive shoppers / in addition / love freebies</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>Khách mua sắm tùy hứng / hơn nữa / thích quà tặng kèm</t>
-        </is>
-      </c>
-      <c r="K8" s="15" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;Khách mua sắm tùy hứng&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;hơn nữa&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;thích quà tặng kèm&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L8" s="9" t="inlineStr">
+      <c r="K8" s="11" t="inlineStr">
+        <is>
+          <t>Khách mua sắm tùy hứng / hơn thế nữa / thích quà tặng kèm</t>
+        </is>
+      </c>
+      <c r="L8" s="17" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;Khách mua sắm tùy hứng&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;hơn thế nữa&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;thích quà tặng kèm&lt;/s&gt;&lt;/speak&gt;</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="M8" s="11" t="inlineStr">
+      <c r="N8" s="11" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -5185,27 +5784,32 @@
       <c r="H9" s="5" t="n">
         <v>53.2</v>
       </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>window shoppers / then / buy online later</t>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>Người dạo phố ngắm đồ / sau đó / quay lại mua online</t>
-        </is>
-      </c>
-      <c r="K9" s="14" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;Người dạo phố ngắm đồ&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;sau đó&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;quay lại mua online&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
+          <t>window shoppers / then now / buy online later</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Người dạo phố ngắm đồ / sau đó liền / quay lại mua online</t>
+        </is>
+      </c>
+      <c r="L9" s="16" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;Người dạo phố ngắm đồ&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;sau đó liền&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;quay lại mua online&lt;/s&gt;&lt;/speak&gt;</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="M9" s="7" t="inlineStr">
+      <c r="N9" s="7" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -5240,27 +5844,32 @@
       <c r="H10" s="9" t="n">
         <v>53.2</v>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>shopping platform / for instance / embeds livestream</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>Nền tảng mua bán / ví dụ / tích hợp livestream</t>
-        </is>
-      </c>
-      <c r="K10" s="15" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;Nền tảng mua bán&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;ví dụ&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;tích hợp livestream&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L10" s="9" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
+        <is>
+          <t>Nền tảng mua bán / ví dụ như / tích hợp livestream</t>
+        </is>
+      </c>
+      <c r="L10" s="17" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;Nền tảng mua bán&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;ví dụ như&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;tích hợp livestream&lt;/s&gt;&lt;/speak&gt;</t>
+        </is>
+      </c>
+      <c r="M10" s="9" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -5295,27 +5904,32 @@
       <c r="H11" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>Why / moreover / shopaholic instinct / overspend wildly</t>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>Vì sao / hơn nữa / con nghiện mua sắm / vung tay quá trán</t>
-        </is>
-      </c>
-      <c r="K11" s="14" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;Vì sao&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;hơn nữa&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;con nghiện mua sắm&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;vung tay quá trán&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
+          <t>Why now / moreover now / shopaholic instinct / overspend wildly</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>Lý do vì sao / hơn thế nữa / con nghiện mua sắm / vung tay quá trán</t>
+        </is>
+      </c>
+      <c r="L11" s="16" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;Lý do vì sao&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;hơn thế nữa&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;con nghiện mua sắm&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;vung tay quá trán&lt;/s&gt;&lt;/speak&gt;</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="M11" s="7" t="inlineStr">
+      <c r="N11" s="7" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -5350,27 +5964,32 @@
       <c r="H12" s="9" t="n">
         <v>53</v>
       </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>window shopping stroll / then / sweet bait / trigger instant buy</t>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>Đi lượn lờ ngắm đồ / sau đó / mồi câu hấp dẫn / khiến chốt đơn ngay</t>
-        </is>
-      </c>
-      <c r="K12" s="15" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;Đi lượn lờ ngắm đồ&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;sau đó&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;mồi câu hấp dẫn&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;khiến chốt đơn ngay&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L12" s="9" t="inlineStr">
+          <t>window shopping stroll / then now / sweet bait / trigger instant buy</t>
+        </is>
+      </c>
+      <c r="K12" s="11" t="inlineStr">
+        <is>
+          <t>Đi lượn lờ ngắm đồ / sau đó liền / mồi câu hấp dẫn / khiến chốt đơn ngay</t>
+        </is>
+      </c>
+      <c r="L12" s="17" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;Đi lượn lờ ngắm đồ&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;sau đó liền&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;mồi câu hấp dẫn&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;khiến chốt đơn ngay&lt;/s&gt;&lt;/speak&gt;</t>
+        </is>
+      </c>
+      <c r="M12" s="9" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="M12" s="11" t="inlineStr">
+      <c r="N12" s="11" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -5405,27 +6024,32 @@
       <c r="H13" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>stuffed cart / instead / FOMO fever / rush to checkout</t>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
+          <t>stuffed cart / instead of that / FOMO fever / rush to checkout</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
           <t>Giỏ hàng đầy ắp / thay vào đó / nỗi sợ bỏ lỡ / thúc giục thanh toán</t>
         </is>
       </c>
-      <c r="K13" s="14" t="inlineStr">
+      <c r="L13" s="16" t="inlineStr">
         <is>
           <t>&lt;speak&gt;&lt;s&gt;Giỏ hàng đầy ắp&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;thay vào đó&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;nỗi sợ bỏ lỡ&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;thúc giục thanh toán&lt;/s&gt;&lt;/speak&gt;</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr">
+      <c r="M13" s="5" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="M13" s="7" t="inlineStr">
+      <c r="N13" s="7" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -5460,27 +6084,32 @@
       <c r="H14" s="9" t="n">
         <v>58</v>
       </c>
-      <c r="I14" s="11" t="inlineStr">
-        <is>
-          <t>shopping cart / overflowing</t>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>Giỏ hàng trực tuyến / chất đầy ắp</t>
-        </is>
-      </c>
-      <c r="K14" s="15" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;shopping cart&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;overflowing&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L14" s="9" t="inlineStr">
+          <t>shopping cart / overflowing now</t>
+        </is>
+      </c>
+      <c r="K14" s="11" t="inlineStr">
+        <is>
+          <t>Giỏ hàng trực tuyến / chất đầy ắp giỏ</t>
+        </is>
+      </c>
+      <c r="L14" s="17" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;shopping cart&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;overflowing now&lt;/s&gt;&lt;/speak&gt;</t>
+        </is>
+      </c>
+      <c r="M14" s="9" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="M14" s="11" t="inlineStr">
+      <c r="N14" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -5515,27 +6144,32 @@
       <c r="H15" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>sales funnel / optimized</t>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>Phễu bán hàng / tối ưu hóa</t>
-        </is>
-      </c>
-      <c r="K15" s="14" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;sales funnel&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;optimized&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
+          <t>sales funnel / optimized now</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>Phễu bán hàng / tối ưu hóa phễu</t>
+        </is>
+      </c>
+      <c r="L15" s="16" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;sales funnel&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;optimized now&lt;/s&gt;&lt;/speak&gt;</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="M15" s="7" t="inlineStr">
+      <c r="N15" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -5570,27 +6204,32 @@
       <c r="H16" s="9" t="n">
         <v>58</v>
       </c>
-      <c r="I16" s="11" t="inlineStr">
-        <is>
-          <t>conversion rate / skyrocket</t>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>Tỉ lệ chuyển đổi đơn / tăng vọt</t>
-        </is>
-      </c>
-      <c r="K16" s="15" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;conversion rate&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;skyrocket&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L16" s="9" t="inlineStr">
+          <t>conversion rate / skyrocket now</t>
+        </is>
+      </c>
+      <c r="K16" s="11" t="inlineStr">
+        <is>
+          <t>Tỉ lệ chuyển đổi đơn / tăng vọt kỷ lục</t>
+        </is>
+      </c>
+      <c r="L16" s="17" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;conversion rate&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;skyrocket now&lt;/s&gt;&lt;/speak&gt;</t>
+        </is>
+      </c>
+      <c r="M16" s="9" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="M16" s="11" t="inlineStr">
+      <c r="N16" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -5625,27 +6264,32 @@
       <c r="H17" s="5" t="n">
         <v>55.8</v>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>items in cart / as long as / in stock</t>
         </is>
       </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>Sản phẩm trong giỏ hàng / miễn là / còn đủ số lượng</t>
-        </is>
-      </c>
-      <c r="K17" s="14" t="inlineStr">
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>Sản phẩm trong giỏ hàng / miễn là như vậy / còn đủ số lượng</t>
+        </is>
+      </c>
+      <c r="L17" s="16" t="inlineStr">
         <is>
           <t>&lt;speak&gt;&lt;s&gt;items in cart&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;as long as&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;in stock&lt;/s&gt;&lt;/speak&gt;</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="M17" s="5" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="M17" s="7" t="inlineStr">
+      <c r="N17" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -5680,27 +6324,32 @@
       <c r="H18" s="9" t="n">
         <v>55.8</v>
       </c>
-      <c r="I18" s="11" t="inlineStr">
-        <is>
-          <t>funnel optimization / eventually / double sales</t>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>Tối ưu phễu chuyển đổi / sau cùng / nhân đôi doanh thu</t>
-        </is>
-      </c>
-      <c r="K18" s="15" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;funnel optimization&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;eventually&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;double sales&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L18" s="9" t="inlineStr">
+          <t>funnel optimization / eventually now / double sales</t>
+        </is>
+      </c>
+      <c r="K18" s="11" t="inlineStr">
+        <is>
+          <t>Tối ưu phễu chuyển đổi / sau cùng thì / nhân đôi doanh thu</t>
+        </is>
+      </c>
+      <c r="L18" s="17" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;funnel optimization&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;eventually now&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;double sales&lt;/s&gt;&lt;/speak&gt;</t>
+        </is>
+      </c>
+      <c r="M18" s="9" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="M18" s="11" t="inlineStr">
+      <c r="N18" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -5735,27 +6384,32 @@
       <c r="H19" s="5" t="n">
         <v>55.8</v>
       </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>cashless payments / because / supremely convenient</t>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>Giao dịch không tiền mặt / bởi vì / tiện lợi vượt trội</t>
-        </is>
-      </c>
-      <c r="K19" s="14" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;cashless payments&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;because&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;supremely convenient&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
+          <t>cashless payments / because now / supremely convenient</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>Giao dịch không tiền mặt / bởi vì thế / tiện lợi vượt trội</t>
+        </is>
+      </c>
+      <c r="L19" s="16" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;cashless payments&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;because now&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;supremely convenient&lt;/s&gt;&lt;/speak&gt;</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr">
+      <c r="N19" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -5790,27 +6444,32 @@
       <c r="H20" s="9" t="n">
         <v>51.6</v>
       </c>
-      <c r="I20" s="11" t="inlineStr">
-        <is>
-          <t>How long / if / data leak breach / lose trust entirely</t>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J20" s="11" t="inlineStr">
         <is>
-          <t>Bao lâu / nếu / rò rỉ dữ liệu / mất hết uy tín</t>
-        </is>
-      </c>
-      <c r="K20" s="15" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;How long&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;if&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;data leak breach&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;lose trust entirely&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L20" s="9" t="inlineStr">
+          <t>How long / if now / data leak breach / lose trust entirely</t>
+        </is>
+      </c>
+      <c r="K20" s="11" t="inlineStr">
+        <is>
+          <t>Bao lâu / nếu không cẩn thận / rò rỉ dữ liệu / mất hết uy tín</t>
+        </is>
+      </c>
+      <c r="L20" s="17" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;How long&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;if now&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;data leak breach&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;lose trust entirely&lt;/s&gt;&lt;/speak&gt;</t>
+        </is>
+      </c>
+      <c r="M20" s="9" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="M20" s="11" t="inlineStr">
+      <c r="N20" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -5845,27 +6504,32 @@
       <c r="H21" s="5" t="n">
         <v>51.6</v>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>smart sales funnel / so that / cash generator machine / run on autopilot</t>
         </is>
       </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>Phễu bán hàng hiện đại / cho nên / cỗ máy in tiền / hoạt động tự động</t>
-        </is>
-      </c>
-      <c r="K21" s="14" t="inlineStr">
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>Phễu bán hàng hiện đại / cho nên vì thế / cỗ máy in tiền / hoạt động tự động</t>
+        </is>
+      </c>
+      <c r="L21" s="16" t="inlineStr">
         <is>
           <t>&lt;speak&gt;&lt;s&gt;smart sales funnel&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;so that&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;cash generator machine&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;run on autopilot&lt;/s&gt;&lt;/speak&gt;</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="M21" s="5" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="M21" s="7" t="inlineStr">
+      <c r="N21" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -5900,27 +6564,32 @@
       <c r="H22" s="9" t="n">
         <v>51.6</v>
       </c>
-      <c r="I22" s="11" t="inlineStr">
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
+        </is>
+      </c>
+      <c r="J22" s="11" t="inlineStr">
         <is>
           <t>conversion rate / in contrast / vital heartbeat / make or break</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr">
-        <is>
-          <t>Tỉ lệ chuyển đổi đơn / trái lại / thước đo sinh tử / quyết định sống còn</t>
-        </is>
-      </c>
-      <c r="K22" s="15" t="inlineStr">
+      <c r="K22" s="11" t="inlineStr">
+        <is>
+          <t>Tỉ lệ chuyển đổi đơn / trái lại hoàn toàn / thước đo sinh tử / quyết định sống còn</t>
+        </is>
+      </c>
+      <c r="L22" s="17" t="inlineStr">
         <is>
           <t>&lt;speak&gt;&lt;s&gt;conversion rate&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;in contrast&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;vital heartbeat&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;make or break&lt;/s&gt;&lt;/speak&gt;</t>
         </is>
       </c>
-      <c r="L22" s="9" t="inlineStr">
+      <c r="M22" s="9" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="M22" s="11" t="inlineStr">
+      <c r="N22" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -5955,27 +6624,32 @@
       <c r="H23" s="5" t="n">
         <v>55.2</v>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>free ship coupon / as long as / psychological nudge / seal the deal</t>
         </is>
       </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>Mã miễn phí giao hàng / miễn là / cú hích tâm lý / thuyết phục khách mua</t>
-        </is>
-      </c>
-      <c r="K23" s="14" t="inlineStr">
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>Mã miễn phí giao hàng / miễn là như vậy / cú hích tâm lý / thuyết phục khách mua</t>
+        </is>
+      </c>
+      <c r="L23" s="16" t="inlineStr">
         <is>
           <t>&lt;speak&gt;&lt;s&gt;free ship coupon&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;as long as&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;psychological nudge&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;seal the deal&lt;/s&gt;&lt;/speak&gt;</t>
         </is>
       </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="M23" s="5" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="M23" s="7" t="inlineStr">
+      <c r="N23" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -6010,27 +6684,32 @@
       <c r="H24" s="9" t="n">
         <v>55.2</v>
       </c>
-      <c r="I24" s="11" t="inlineStr">
-        <is>
-          <t>superfast delivery / next / killer feature / crush competition</t>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr">
         <is>
-          <t>Giao hàng hỏa tốc / tiếp theo / vũ khí sát thương / đánh bạt đối thủ</t>
-        </is>
-      </c>
-      <c r="K24" s="15" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;superfast delivery&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;next&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;killer feature&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;crush competition&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L24" s="9" t="inlineStr">
+          <t>superfast delivery / next now / killer feature / crush competition</t>
+        </is>
+      </c>
+      <c r="K24" s="11" t="inlineStr">
+        <is>
+          <t>Giao hàng hỏa tốc / tiếp theo đó / vũ khí sát thương / đánh bạt đối thủ</t>
+        </is>
+      </c>
+      <c r="L24" s="17" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;superfast delivery&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;next now&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;killer feature&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;crush competition&lt;/s&gt;&lt;/speak&gt;</t>
+        </is>
+      </c>
+      <c r="M24" s="9" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="M24" s="11" t="inlineStr">
+      <c r="N24" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -6065,27 +6744,32 @@
       <c r="H25" s="5" t="n">
         <v>55.2</v>
       </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>Where / meanwhile / promised land / rural e-commerce</t>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>✓ Zero Single Words (≥2w)</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>Ở đâu / đồng thời / vùng đất hứa / thương mại nông thôn</t>
-        </is>
-      </c>
-      <c r="K25" s="14" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;s&gt;Where&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;meanwhile&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;promised land&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;rural e-commerce&lt;/s&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
+          <t>Where now / meanwhile now / promised land / rural e-commerce</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>ở bất cứ đâu / đồng thời cùng lúc / vùng đất hứa / thương mại nông thôn</t>
+        </is>
+      </c>
+      <c r="L25" s="16" t="inlineStr">
+        <is>
+          <t>&lt;speak&gt;&lt;s&gt;Where now&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;meanwhile now&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;promised land&lt;/s&gt; &lt;break time="650ms"/&gt; &lt;s&gt;rural e-commerce&lt;/s&gt;&lt;/speak&gt;</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="M25" s="7" t="inlineStr">
+      <c r="N25" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -6102,7 +6786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L87"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="49" customWidth="1" min="1" max="1"/>
@@ -6115,8 +6799,9 @@
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="65" customWidth="1" min="9" max="9"/>
     <col width="65" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6180,10 +6865,15 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
+          <t>VI Word Count</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
           <t>Audio Lang</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>Voice Model</t>
         </is>
@@ -6220,20 +6910,25 @@
       </c>
       <c r="I4" s="11" t="inlineStr">
         <is>
-          <t>The e-commerce industry is fiercely competitive in this modern market.</t>
+          <t>The e-commerce industry is fiercely competitive in modern markets.</t>
         </is>
       </c>
       <c r="J4" s="11" t="inlineStr">
         <is>
-          <t>Ngành thương mại điện tử cạnh tranh rất khốc liệt trong thị trường hiện đại.</t>
+          <t>Ngành thương mại điện tử cạnh tranh rất khốc liệt.</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
         <is>
+          <t>10 từ</t>
+        </is>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L4" s="11" t="inlineStr">
+      <c r="M4" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -6270,20 +6965,25 @@
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Many online shoppers stay up late for midnight deal hunting.</t>
+          <t>Many shoppers stay up late for midnight discount sales.</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>Nhiều người mua sắm trực tuyến thức trắng đêm để săn sale nửa đêm.</t>
+          <t>Nhiều người thức trắng đêm để săn sale giảm giá.</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
+          <t>10 từ</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -6320,20 +7020,25 @@
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
-          <t>My digital wallet is securely linked to my local bank account.</t>
+          <t>The digital wallet is safely linked to bank accounts.</t>
         </is>
       </c>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>Ví điện tử của tôi đã được liên kết an toàn với tài khoản ngân hàng.</t>
+          <t>Ví điện tử đã được liên kết với ngân hàng.</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
+          <t>10 từ</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L6" s="11" t="inlineStr">
+      <c r="M6" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -6370,20 +7075,25 @@
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Competitive pricing always helps new online stores draw customers.</t>
+          <t>Competitive pricing always helps retail shops draw active customers.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>Mức giá cạnh tranh luôn giúp các cửa hàng trực tuyến thu hút khách mua.</t>
+          <t>Mức giá cạnh tranh luôn giúp cửa hàng thu hút khách mua.</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
+          <t>12 từ</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L7" s="7" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -6420,20 +7130,25 @@
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
-          <t>I often enjoy casual window shopping on mobile apps to unwind after work.</t>
+          <t>I often enjoy casual window shopping online to relieve stress.</t>
         </is>
       </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>Tôi thường dạo ngắm đồ trên ứng dụng điện thoại để xả stress sau giờ làm.</t>
+          <t>Tôi thường dạo ngắm đồ trên mạng để giải tỏa căng thẳng.</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
         <is>
+          <t>12 từ</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L8" s="11" t="inlineStr">
+      <c r="M8" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -6470,20 +7185,25 @@
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>Her virtual shopping cart is already overflowing with seasonal discounts.</t>
+          <t>Her virtual shopping cart is overflowing with great discounted products.</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>Giỏ hàng trực tuyến của cô ấy đã đầy ắp các món đồ giảm giá theo mùa.</t>
+          <t>Giỏ hàng trực tuyến của cô ấy đầy ắp đồ giảm giá.</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
+          <t>12 từ</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L9" s="7" t="inlineStr">
+      <c r="M9" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -6520,20 +7240,25 @@
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
-          <t>The platform hyped up the flash sale drive, so millions of shoppers joined early.</t>
+          <t>The flash sale was hyped up, so customers placed orders very early.</t>
         </is>
       </c>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>Nền tảng đã quảng bá rầm rộ chiến dịch săn sale, vì thế hàng triệu người tham gia từ sớm.</t>
+          <t>Chiến dịch săn sale được quảng bá rầm rộ nên khách đặt mua sớm.</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
         <is>
+          <t>14 từ</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -6570,20 +7295,25 @@
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>You should complete your e-wallet checkout today, and you will get instant cashback.</t>
+          <t>When checking out with an e-wallet, you receive cashback instantly.</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>Bạn nên hoàn tất thanh toán bằng ví điện tử hôm nay, và bạn sẽ nhận được tiền hoàn ngay lập tức.</t>
+          <t>Khi thanh toán bằng ví điện tử, bạn sẽ nhận được tiền hoàn ngay.</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
+          <t>14 từ</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L11" s="7" t="inlineStr">
+      <c r="M11" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -6620,20 +7350,25 @@
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>Review the items in your cart carefully, as long as they are still in stock.</t>
+          <t>Check your shopping cart carefully while selected items are still in stock.</t>
         </is>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>Hãy kiểm tra kỹ các sản phẩm trong giỏ hàng, miễn là chúng vẫn còn đủ số lượng.</t>
+          <t>Bạn nên kiểm tra giỏ hàng cẩn thận khi sản phẩm còn đủ hàng.</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
         <is>
+          <t>14 từ</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L12" s="11" t="inlineStr">
+      <c r="M12" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -6670,20 +7405,25 @@
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>Cashless payments are supremely convenient, and modern consumers increasingly prefer them.</t>
+          <t>Cashless payments are very convenient, so consumers increasingly prefer shopping online.</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>Phương thức thanh toán không tiền mặt rất tiện lợi, và người tiêu dùng ngày càng ưa chuộng nó.</t>
+          <t>Thanh toán không tiền mặt rất thuận tiện, nên người dùng ngày càng chuộng mua sắm.</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
+          <t>16 từ</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L13" s="7" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -6720,20 +7460,25 @@
       </c>
       <c r="I14" s="11" t="inlineStr">
         <is>
-          <t>The shop offers a free shipping coupon, so customers quickly place more orders.</t>
+          <t>The store offers free shipping codes, helping buyers quickly place more orders.</t>
         </is>
       </c>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>Cửa hàng tặng kèm mã miễn phí vận chuyển, do đó khách hàng nhanh chóng đặt thêm nhiều đơn mới.</t>
+          <t>Cửa hàng tặng mã miễn phí vận chuyển, giúp khách nhanh chóng chốt thêm nhiều đơn.</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
         <is>
+          <t>16 từ</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L14" s="11" t="inlineStr">
+      <c r="M14" s="11" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -6770,20 +7515,25 @@
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>Instant delivery service is highly popular, but the company must expand nationwide.</t>
+          <t>Instant delivery service is great, but companies need to expand their network.</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>Dịch vụ giao hàng hỏa tốc đang rất được yêu thích, nhưng công ty cần mở rộng trên toàn quốc.</t>
+          <t>Dịch vụ giao hàng hỏa tốc rất tốt, nhưng doanh nghiệp cần mở rộng mạng lưới.</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
+          <t>16 từ</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L15" s="7" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -6820,20 +7570,25 @@
       </c>
       <c r="I16" s="11" t="inlineStr">
         <is>
-          <t>Although advertising costs have risen, systematically optimizing the sales funnel helped the brand double its revenue.</t>
+          <t>Although advertising costs have risen, sales funnel optimization helps significantly increase revenue.</t>
         </is>
       </c>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>Mặc dù chi phí quảng cáo tăng cao, việc tối ưu phễu chuyển đổi bài bản đã giúp doanh nghiệp nhân đôi doanh số.</t>
+          <t>Dù chi phí quảng cáo tăng cao, việc tối ưu phễu bán hàng giúp tăng mạnh doanh thu.</t>
         </is>
       </c>
       <c r="K16" s="9" t="inlineStr">
         <is>
+          <t>18 từ</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L16" s="11" t="inlineStr">
+      <c r="M16" s="11" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -6870,20 +7625,25 @@
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>By providing attractive loyalty rewards, the brand can successfully retain its valuable customer base over the long run.</t>
+          <t>By applying attractive loyalty programs, the brand successfully retained many regular customers.</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>Bằng cách cung cấp các chương trình tích điểm tri ân hấp dẫn, thương hiệu có thể giữ chân lượng khách hàng trung thành dài lâu.</t>
+          <t>Nhờ áp dụng chương trình tri ân hấp dẫn, thương hiệu đã giữ chân được nhiều khách quen.</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
+          <t>18 từ</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L17" s="7" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -6920,20 +7680,25 @@
       </c>
       <c r="I18" s="11" t="inlineStr">
         <is>
-          <t>When the midnight shopping frenzy suddenly erupted, the engineering team had to monitor continuously so that the servers would not crash.</t>
+          <t>When the shopping frenzy erupted, engineers monitored servers all night to keep them running.</t>
         </is>
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>Khi cơn sốt mua sắm nửa đêm bất ngờ bùng nổ, đội ngũ kỹ thuật phải ứng trực liên tục để hệ thống máy chủ không bị sập.</t>
+          <t>Khi cơn sốt mua sắm bùng nổ, các kỹ sư phải túc trực đêm để giữ máy chủ.</t>
         </is>
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
+          <t>18 từ</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L18" s="11" t="inlineStr">
+      <c r="M18" s="11" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -6970,20 +7735,25 @@
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>In e-commerce operations, the checkout conversion rate serves as the vital metric that determines overall financial viability.</t>
+          <t>In e-commerce, the checkout conversion rate is a vital metric that determines overall business success.</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>Trong kinh doanh thương mại điện tử, tỉ lệ chuyển đổi đơn hàng là thước đo sống còn quyết định toàn bộ hiệu quả tài chính.</t>
+          <t>Trong thương mại điện tử, tỉ lệ chuyển đổi là thước đo sống còn quyết định toàn bộ thành công.</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
+          <t>20 từ</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L19" s="7" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -7020,20 +7790,25 @@
       </c>
       <c r="I20" s="11" t="inlineStr">
         <is>
-          <t>If brands impose excessive express delivery fees, it becomes a major stumbling block that prompts immediate cart abandonment.</t>
+          <t>If sellers charge excessive shipping fees, customers will immediately abandon their shopping carts.</t>
         </is>
       </c>
       <c r="J20" s="11" t="inlineStr">
         <is>
-          <t>Nếu thương hiệu áp đặt phí vận chuyển quá đắt đỏ, điều đó sẽ trở thành rào cản lớn khiến khách hàng lập tức bỏ quên giỏ hàng.</t>
+          <t>Nếu người bán tính phí vận chuyển quá đắt đỏ, khách hàng sẽ lập tức từ bỏ giỏ hàng.</t>
         </is>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
+          <t>19 từ</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L20" s="11" t="inlineStr">
+      <c r="M20" s="11" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -7070,20 +7845,25 @@
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>A transparent seven-day return guarantee not only establishes robust consumer trust, but also provides total peace of mind before checkout.</t>
+          <t>A seven-day return policy not only builds reputation, but also gives buyers great peace of mind.</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>Chính sách đổi trả minh bạch trong bảy ngày không chỉ tạo dựng niềm tin vững chắc, mà còn giúp người mua hoàn toàn yên tâm chốt đơn.</t>
+          <t>Chính sách đổi trả bảy ngày không chỉ tạo dựng uy tín, mà còn giúp khách hàng rất an tâm.</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
+          <t>20 từ</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L21" s="7" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -7120,20 +7900,25 @@
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
-          <t>While the e-commerce arena remains a highly lucrative market, entering an unsustainable cash-burning war will inevitably drain your capital reserves.</t>
+          <t>The retail market is lucrative, but continuous cash burning will inevitably drain an enterprise of capital reserves.</t>
         </is>
       </c>
       <c r="J22" s="11" t="inlineStr">
         <is>
-          <t>Mặc dù thị trường thương mại điện tử là một miếng bánh vô cùng màu mỡ, việc bước vào cuộc chiến đốt tiền không bền vững chắc chắn sẽ làm cạn kiệt nguồn vốn dự trữ.</t>
+          <t>Thị trường thương mại rất màu mỡ, nhưng nếu liên tục đốt tiền thì doanh nghiệp sẽ sớm cạn kiệt nguồn vốn.</t>
         </is>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
+          <t>22 từ</t>
+        </is>
+      </c>
+      <c r="L22" s="9" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L22" s="11" t="inlineStr">
+      <c r="M22" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -7170,20 +7955,25 @@
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>By integrating interactive live shopping shows directly into the platform, retail merchants can captivate impulsive shoppers and achieve extraordinary checkout velocity.</t>
+          <t>Hosting live sales streams directly on apps attracts shoppers and achieves remarkably rapid checkout speeds.</t>
         </is>
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>Bằng cách tích hợp các phiên livestream bán hàng tương tác trực tiếp lên nền tảng, nhà bán lẻ có thể thu hút khách mua sắm tùy hứng và đạt tốc độ chốt đơn vượt bậc.</t>
+          <t>Việc tổ chức livestream bán hàng trực tiếp trên ứng dụng giúp thu hút khách mua và chốt đơn rất nhanh chóng.</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
+          <t>22 từ</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L23" s="7" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -7220,20 +8010,25 @@
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>To thrive amid aggressive price competition, retail brands must cultivate an omnichannel presence that reinforces customer loyalty and safeguards long-term profit margins.</t>
+          <t>To compete effectively in digital markets, retail brands must build sustainable omnichannel sales models.</t>
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr">
         <is>
-          <t>Để phát triển bền vững trước cuộc cạnh tranh giá khốc liệt, các thương hiệu bán lẻ phải xây dựng mô hình đa kênh giúp gia tăng lòng trung thành và bảo vệ biên lợi nhuận dài hạn.</t>
+          <t>Để cạnh tranh trên thị trường số, các thương hiệu cần xây dựng mô hình bán lẻ đa kênh bền vững.</t>
         </is>
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
+          <t>21 từ</t>
+        </is>
+      </c>
+      <c r="L24" s="9" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L24" s="11" t="inlineStr">
+      <c r="M24" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -7270,20 +8065,25 @@
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>An impulsive shopper often loves to buy on impulse during holiday sales.</t>
+          <t>An impulsive shopper often picks items based on pure emotion.</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>Người tiêu dùng tùy hứng thường thích chốt đơn nhanh vào các dịp lễ hội.</t>
+          <t>Người mua tùy hứng thường chọn đồ theo cảm xúc.</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
+          <t>10 từ</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L25" s="7" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -7320,20 +8120,25 @@
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>This vibrant marketplace continues to grow rapidly with thousands of new sellers.</t>
+          <t>This retail marketplace continues to grow at an extraordinary speed.</t>
         </is>
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>Thị trường sôi động này tiếp tục tăng trưởng nóng với hàng ngàn người bán mới.</t>
+          <t>Thị trường bán lẻ này tăng trưởng vô cùng nhanh.</t>
         </is>
       </c>
       <c r="K26" s="9" t="inlineStr">
         <is>
+          <t>10 từ</t>
+        </is>
+      </c>
+      <c r="L26" s="9" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L26" s="11" t="inlineStr">
+      <c r="M26" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -7370,20 +8175,25 @@
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>A simple and secure checkout process makes online shopping very pleasant.</t>
+          <t>A secure checkout process helps you feel completely confident.</t>
         </is>
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>Quy trình thanh toán an toàn và đơn giản khiến việc mua hàng online rất dễ chịu.</t>
+          <t>Quy trình thanh toán an toàn giúp bạn an tâm.</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
+          <t>10 từ</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L27" s="7" t="inlineStr">
+      <c r="M27" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -7420,20 +8230,25 @@
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t>Customers can easily track their package delivery in real time on mobile.</t>
+          <t>Customers can easily track their package journey on mobile phones.</t>
         </is>
       </c>
       <c r="J28" s="11" t="inlineStr">
         <is>
-          <t>Khách hàng có thể dễ dàng theo dõi hành trình bưu kiện theo thời gian thực trên điện thoại.</t>
+          <t>Khách hàng dễ dàng theo dõi hành trình đơn trên điện thoại.</t>
         </is>
       </c>
       <c r="K28" s="9" t="inlineStr">
         <is>
+          <t>12 từ</t>
+        </is>
+      </c>
+      <c r="L28" s="9" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L28" s="11" t="inlineStr">
+      <c r="M28" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -7470,20 +8285,25 @@
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>Reading genuine product reviews helps me choose trustworthy shops with five stars.</t>
+          <t>Reading genuine product reviews helps shoppers choose reputable online stores.</t>
         </is>
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>Đọc đánh giá sản phẩm thực tế giúp tôi chọn được các cửa hàng năm sao uy tín.</t>
+          <t>Đọc nhận xét thực tế giúp chọn được cửa hàng uy tín.</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
+          <t>12 từ</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L29" s="7" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -7520,20 +8340,25 @@
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
-          <t>Do not forget to apply your discount voucher before making final payment.</t>
+          <t>Do not forget to apply your discount voucher before confirming your order.</t>
         </is>
       </c>
       <c r="J30" s="11" t="inlineStr">
         <is>
-          <t>Đừng quên nhập mã giảm giá ưu đãi trước khi tiến hành thanh toán cuối cùng.</t>
+          <t>Đừng quên nhập mã giảm giá trước khi bạn xác nhận đơn.</t>
         </is>
       </c>
       <c r="K30" s="9" t="inlineStr">
         <is>
+          <t>12 từ</t>
+        </is>
+      </c>
+      <c r="L30" s="9" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L30" s="11" t="inlineStr">
+      <c r="M30" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -7570,20 +8395,25 @@
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>Impulsive shoppers love freebies, so we added exclusive gifts to each order.</t>
+          <t>Shoppers love promotional gifts, so the shop added small freebies to orders.</t>
         </is>
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>Khách mua hàng rất thích quà tặng kèm, vì vậy chúng tôi đã thêm ưu đãi vào đơn.</t>
+          <t>Khách mua hàng rất thích quà tặng, nên cửa hàng tặng thêm quà nhỏ.</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
+          <t>14 từ</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="M31" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -7620,20 +8450,25 @@
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
-          <t>Many people browse items in store windows during the day, and then they buy online at night.</t>
+          <t>Many people only browse items by day, but buy online at night.</t>
         </is>
       </c>
       <c r="J32" s="11" t="inlineStr">
         <is>
-          <t>Nhiều người dạo ngắm đồ trên phố ban ngày, rồi sau đó họ đặt mua trực tuyến vào ban đêm.</t>
+          <t>Nhiều người chỉ ngắm đồ ban ngày, nhưng lại đặt mua vào ban đêm.</t>
         </is>
       </c>
       <c r="K32" s="9" t="inlineStr">
         <is>
+          <t>14 từ</t>
+        </is>
+      </c>
+      <c r="L32" s="9" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L32" s="11" t="inlineStr">
+      <c r="M32" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -7670,20 +8505,25 @@
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>The modern shopping platform embeds live video, so buyers can interact directly with sellers.</t>
+          <t>The shopping application integrates live video, helping buyers interact very easily.</t>
         </is>
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>Nền tảng mua sắm hiện nay tích hợp livestream, giúp người tiêu dùng tương tác trực tiếp với người bán.</t>
+          <t>Ứng dụng mua sắm tích hợp video giúp người mua tương tác dễ dàng.</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
+          <t>14 từ</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L33" s="7" t="inlineStr">
+      <c r="M33" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -7720,20 +8560,25 @@
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t>The wholesale distributor prioritizes high volume, yet they still maintain very competitive rates.</t>
+          <t>The wholesale distributor prioritizes high volume, yet they still maintain very competitive pricing.</t>
         </is>
       </c>
       <c r="J34" s="11" t="inlineStr">
         <is>
-          <t>Nhà phân phối bán sỉ luôn ưu tiên số lượng lớn, nhưng họ vẫn duy trì mức giá rất cạnh tranh.</t>
+          <t>Nhà phân phối bán sỉ ưu tiên số lượng, nhưng vẫn giữ giá rất cạnh tranh.</t>
         </is>
       </c>
       <c r="K34" s="9" t="inlineStr">
         <is>
+          <t>16 từ</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L34" s="11" t="inlineStr">
+      <c r="M34" s="11" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -7770,20 +8615,25 @@
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>The interactive live session attracted thousands of viewers, and the shop sold out within half an hour.</t>
+          <t>The interactive live stream was crowded, and the shop completely sold out of everything.</t>
         </is>
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>Buổi tương tác trực tuyến thu hút hàng ngàn lượt xem, và cửa hàng đã bán hết sạch hàng chỉ sau nửa giờ.</t>
+          <t>Buổi tương tác trực tuyến rất đông, và cửa hàng đã bán sạch hết mọi thứ.</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
+          <t>16 từ</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L35" s="7" t="inlineStr">
+      <c r="M35" s="7" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -7820,20 +8670,25 @@
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
-          <t>The mobile app just pushed a flash discount notification, so buyers immediately checked their phones.</t>
+          <t>The system just sent discount notifications, so shoppers immediately opened the app.</t>
         </is>
       </c>
       <c r="J36" s="11" t="inlineStr">
         <is>
-          <t>Ứng dụng vừa gửi thông báo giảm giá sốc, do đó người mua ngay lập tức mở điện thoại để săn đồ.</t>
+          <t>Hệ thống vừa gửi thông báo giảm giá, do đó người mua lập tức mở app.</t>
         </is>
       </c>
       <c r="K36" s="9" t="inlineStr">
         <is>
+          <t>16 từ</t>
+        </is>
+      </c>
+      <c r="L36" s="9" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L36" s="11" t="inlineStr">
+      <c r="M36" s="11" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -7870,20 +8725,25 @@
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>Because top brands released numerous promotional codes on the shopping festival, order volume skyrocketed to record highs.</t>
+          <t>Because retail brands rolled out massive promotions, order volume skyrocketed to record highs.</t>
         </is>
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>Bởi vì các thương hiệu tung ra hàng loạt mã khuyến mãi vào ngày hội mua sắm, lượng đơn hàng đã tăng vọt kỷ lục.</t>
+          <t>Bởi vì các nhãn hàng tung ra nhiều khuyến mãi, lượng đơn hàng đã tăng vọt kỷ lục.</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
+          <t>18 từ</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L37" s="7" t="inlineStr">
+      <c r="M37" s="7" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -7920,20 +8780,25 @@
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
-          <t>If platforms fail to invest in rigorous payment data security, they will completely lose the hard-earned trust of their users.</t>
+          <t>If platforms fail to secure customer data, they will lose the trust of modern consumers.</t>
         </is>
       </c>
       <c r="J38" s="11" t="inlineStr">
         <is>
-          <t>Nếu nền tảng không đầu tư bảo mật thông tin thanh toán nghiêm ngặt, họ sẽ đánh mất hoàn toàn niềm tin từ cộng đồng người dùng.</t>
+          <t>Nếu sàn không bảo mật dữ liệu khách hàng, họ sẽ mất niềm tin từ người tiêu dùng.</t>
         </is>
       </c>
       <c r="K38" s="9" t="inlineStr">
         <is>
+          <t>18 từ</t>
+        </is>
+      </c>
+      <c r="L38" s="9" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L38" s="11" t="inlineStr">
+      <c r="M38" s="11" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -7970,20 +8835,25 @@
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>By analyzing browsing habits and recommending relevant products, retailers can noticeably increase their average order value.</t>
+          <t>By recommending items matching buyer preferences, merchants can raise average order values.</t>
         </is>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>Bằng cách phân tích hành vi duyệt web và đề xuất sản phẩm phù hợp, cửa hàng có thể nâng cao đáng kể giá trị trung bình trên mỗi đơn.</t>
+          <t>Bằng cách gợi ý sản phẩm hợp sở thích, người bán có thể nâng cao giá trị đơn.</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
+          <t>18 từ</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L39" s="7" t="inlineStr">
+      <c r="M39" s="7" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -8020,20 +8890,25 @@
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
-          <t>Although market competition is exceptionally fierce, a smart affiliate marketing strategy created immense leverage for rapid revenue growth.</t>
+          <t>Although market competition is fierce, affiliate marketing remains a powerful lever for sales growth.</t>
         </is>
       </c>
       <c r="J40" s="11" t="inlineStr">
         <is>
-          <t>Mặc dù thị trường cạnh tranh vô cùng gay gắt, chiến lược tiếp thị liên kết thông minh đã tạo ra đòn bẩy tăng trưởng doanh số vượt bậc.</t>
+          <t>Dù thị trường cạnh tranh gay gắt, tiếp thị liên kết vẫn là đòn bẩy tăng trưởng doanh số mạnh.</t>
         </is>
       </c>
       <c r="K40" s="9" t="inlineStr">
         <is>
+          <t>20 từ</t>
+        </is>
+      </c>
+      <c r="L40" s="9" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L40" s="11" t="inlineStr">
+      <c r="M40" s="11" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -8070,20 +8945,25 @@
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>When negative one-star reviews arise from dissatisfied buyers, customer support must proactively listen and resolve issues to protect brand reputation.</t>
+          <t>When buyers leave negative feedback, staff must quickly resolve issues to protect brand reputation.</t>
         </is>
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>Khi phát sinh các đánh giá một sao từ khách hàng, bộ phận chăm sóc phải chủ động lắng nghe và giải quyết thỏa đáng để bảo vệ danh tiếng.</t>
+          <t>Khi khách để lại đánh giá tiêu cực, nhân viên cần nhanh chóng giải quyết để bảo vệ uy tín.</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
+          <t>20 từ</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L41" s="7" t="inlineStr">
+      <c r="M41" s="7" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -8120,20 +9000,25 @@
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
-          <t>Employing artificial intelligence to personalize shopping carts not only delights consumers, but also substantially optimizes digital marketing expenditures.</t>
+          <t>Employing smart personalization for shopping carts not only delights consumers, but also saves advertising budget.</t>
         </is>
       </c>
       <c r="J42" s="11" t="inlineStr">
         <is>
-          <t>Việc áp dụng công nghệ trí tuệ nhân tạo để cá nhân hóa giỏ hàng không những làm hài lòng khách mua, mà còn tối ưu hóa chi phí tiếp thị.</t>
+          <t>Áp dụng công nghệ cá nhân hóa giỏ hàng không chỉ làm khách hài lòng, mà còn tiết kiệm tiền.</t>
         </is>
       </c>
       <c r="K42" s="9" t="inlineStr">
         <is>
+          <t>20 từ</t>
+        </is>
+      </c>
+      <c r="L42" s="9" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L42" s="11" t="inlineStr">
+      <c r="M42" s="11" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -8170,20 +9055,25 @@
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>By engineering a seamless digital payment ecosystem paired with ultra-fast logistics, leading e-commerce platforms have fundamentally reshaped modern consumer spending habits.</t>
+          <t>By establishing convenient payments alongside instant delivery, online platforms have reshaped consumer shopping habits.</t>
         </is>
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>Nhờ xây dựng một hệ sinh thái thanh toán số liền mạch kết hợp giao hàng siêu tốc, các nền tảng bán lẻ hàng đầu đã tái định hình toàn bộ thói quen chi tiêu của người tiêu dùng.</t>
+          <t>Nhờ hệ thống thanh toán tiện lợi cùng giao hàng hỏa tốc, các sàn đã thay đổi thói quen người mua sắm.</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
+          <t>22 từ</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L43" s="7" t="inlineStr">
+      <c r="M43" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -8220,20 +9110,25 @@
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
-          <t>Although aggressive promotional price cuts generate massive initial traffic surges, top enterprise merchants always prioritize sustainable cash flow and net margin preservation.</t>
+          <t>Although discount waves attract large crowds, smart enterprises always focus on preserving their net profit margins.</t>
         </is>
       </c>
       <c r="J44" s="11" t="inlineStr">
         <is>
-          <t>Mặc dù các đợt giảm giá kích cầu chớp nhoáng có thể mang lại lượng truy cập khổng lồ, những doanh nghiệp xuất sắc luôn ưu tiên bảo toàn biên lợi nhuận ròng và dòng tiền thực tế.</t>
+          <t>Dù các đợt giảm giá mang lại lượng khách lớn, doanh nghiệp giỏi luôn chú trọng bảo toàn biên lợi nhuận.</t>
         </is>
       </c>
       <c r="K44" s="9" t="inlineStr">
         <is>
+          <t>21 từ</t>
+        </is>
+      </c>
+      <c r="L44" s="9" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L44" s="11" t="inlineStr">
+      <c r="M44" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -8270,20 +9165,25 @@
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>In an era of ubiquitous digital commerce, establishing seamless synergy between physical flagship showrooms and online retail touchpoints unlocks unprecedented customer lifetime value.</t>
+          <t>In the digital era, combining physical stores with online platforms helps retail brands grow sustainably long term.</t>
         </is>
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>Trong kỷ nguyên số hóa toàn diện, sự cộng hưởng nhịp nhàng giữa cửa hàng trải nghiệm thực tế và nền tảng mua sắm trực tuyến chính là chìa khóa mở ra tiềm năng tăng trưởng vô tận.</t>
+          <t>Trong thời đại số, kết hợp cửa hàng và sàn trực tuyến giúp thương hiệu phát triển bền vững dài lâu.</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
+          <t>21 từ</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L45" s="7" t="inlineStr">
+      <c r="M45" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -8330,10 +9230,15 @@
       </c>
       <c r="K46" s="9" t="inlineStr">
         <is>
+          <t>2 cụm</t>
+        </is>
+      </c>
+      <c r="L46" s="9" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L46" s="11" t="inlineStr">
+      <c r="M46" s="11" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -8375,15 +9280,20 @@
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>Săn sale nửa đêm / thức trắng</t>
+          <t>Săn sale nửa đêm / thức trắng đêm</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
+          <t>2 cụm</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L47" s="7" t="inlineStr">
+      <c r="M47" s="7" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -8430,10 +9340,15 @@
       </c>
       <c r="K48" s="9" t="inlineStr">
         <is>
+          <t>2 cụm</t>
+        </is>
+      </c>
+      <c r="L48" s="9" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L48" s="11" t="inlineStr">
+      <c r="M48" s="11" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -8470,20 +9385,25 @@
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>e-commerce landscape / however / saturates quickly</t>
+          <t>e-commerce landscape / however now / saturates quickly</t>
         </is>
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>Thị trường thương mại điện tử / tuy nhiên / bão hòa nhanh</t>
+          <t>Thị trường thương mại điện tử / tuy nhiên vậy / bão hòa nhanh</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
+          <t>3 cụm</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L49" s="7" t="inlineStr">
+      <c r="M49" s="7" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -8525,15 +9445,20 @@
       </c>
       <c r="J50" s="11" t="inlineStr">
         <is>
-          <t>Chiến dịch săn sale / trước đó / quảng bá rầm rộ</t>
+          <t>Chiến dịch săn sale / trước đó trước / quảng bá rầm rộ</t>
         </is>
       </c>
       <c r="K50" s="9" t="inlineStr">
         <is>
+          <t>3 cụm</t>
+        </is>
+      </c>
+      <c r="L50" s="9" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L50" s="11" t="inlineStr">
+      <c r="M50" s="11" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -8570,20 +9495,25 @@
       </c>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>e-wallet checkout / meanwhile / get cashback</t>
+          <t>e-wallet checkout / meanwhile now / get cashback</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>Thanh toán ví điện tử / đồng thời / nhận mã hoàn tiền</t>
+          <t>Thanh toán ví điện tử / đồng thời cùng lúc / nhận mã hoàn tiền</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
+          <t>3 cụm</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L51" s="7" t="inlineStr">
+      <c r="M51" s="7" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -8620,20 +9550,25 @@
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
-          <t>e-commerce arena / while / lucrative pie / everyone wants slice</t>
+          <t>e-commerce arena / while now / lucrative pie / everyone wants slice</t>
         </is>
       </c>
       <c r="J52" s="11" t="inlineStr">
         <is>
-          <t>Ngành thương mại điện tử / trong khi / miếng bánh màu mỡ / ai cũng muốn chia phần</t>
+          <t>Ngành thương mại điện tử / trong khi đó / miếng bánh màu mỡ / ai cũng muốn chia phần</t>
         </is>
       </c>
       <c r="K52" s="9" t="inlineStr">
         <is>
+          <t>4 cụm</t>
+        </is>
+      </c>
+      <c r="L52" s="9" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L52" s="11" t="inlineStr">
+      <c r="M52" s="11" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -8670,20 +9605,25 @@
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>When / otherwise / shopping frenzy / crash servers</t>
+          <t>When now / otherwise now / shopping frenzy / crash servers</t>
         </is>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>Khi nào / nếu không / cơn bão săn sale / sẽ làm sập hệ thống</t>
+          <t>Bất cứ khi nào / nếu không thì / cơn bão săn sale / sẽ làm sập hệ thống</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
+          <t>4 cụm</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L53" s="7" t="inlineStr">
+      <c r="M53" s="7" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -8720,20 +9660,25 @@
       </c>
       <c r="I54" s="11" t="inlineStr">
         <is>
-          <t>linked e-wallet / however / customer magnet / boost retention</t>
+          <t>linked e-wallet / however now / customer magnet / boost retention</t>
         </is>
       </c>
       <c r="J54" s="11" t="inlineStr">
         <is>
-          <t>Ví điện tử liên kết / tuy nhiên / thỏi nam châm hút khách / tăng độ gắn kết</t>
+          <t>Ví điện tử liên kết / tuy nhiên vậy / thỏi nam châm hút khách / tăng độ gắn kết</t>
         </is>
       </c>
       <c r="K54" s="9" t="inlineStr">
         <is>
+          <t>4 cụm</t>
+        </is>
+      </c>
+      <c r="L54" s="9" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L54" s="11" t="inlineStr">
+      <c r="M54" s="11" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -8780,10 +9725,15 @@
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
+          <t>2 cụm</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L55" s="7" t="inlineStr">
+      <c r="M55" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -8825,15 +9775,20 @@
       </c>
       <c r="J56" s="11" t="inlineStr">
         <is>
-          <t>Mức giá cạnh tranh / hút khách</t>
+          <t>Mức giá cạnh tranh / thu hút khách mua</t>
         </is>
       </c>
       <c r="K56" s="9" t="inlineStr">
         <is>
+          <t>2 cụm</t>
+        </is>
+      </c>
+      <c r="L56" s="9" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L56" s="11" t="inlineStr">
+      <c r="M56" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -8880,10 +9835,15 @@
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
+          <t>2 cụm</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L57" s="7" t="inlineStr">
+      <c r="M57" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -8920,20 +9880,25 @@
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
-          <t>cash burning tactics / therefore / unsustainable</t>
+          <t>cash burning tactics / therefore now / unsustainable now</t>
         </is>
       </c>
       <c r="J58" s="11" t="inlineStr">
         <is>
-          <t>Chiêu trò đốt tiền / do đó / không bền lâu</t>
+          <t>Chiêu trò đốt tiền / do đó cho nên / không bền lâu dài</t>
         </is>
       </c>
       <c r="K58" s="9" t="inlineStr">
         <is>
+          <t>3 cụm</t>
+        </is>
+      </c>
+      <c r="L58" s="9" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L58" s="11" t="inlineStr">
+      <c r="M58" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -8970,20 +9935,25 @@
       </c>
       <c r="I59" s="7" t="inlineStr">
         <is>
-          <t>competitive pricing / otherwise / lose market share</t>
+          <t>competitive pricing / otherwise now / lose market share</t>
         </is>
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>Chiến lược giá cạnh tranh / nếu không / mất thị phần</t>
+          <t>Chiến lược giá cạnh tranh / nếu không thì / mất thị phần</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
+          <t>3 cụm</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L59" s="7" t="inlineStr">
+      <c r="M59" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -9025,15 +9995,20 @@
       </c>
       <c r="J60" s="11" t="inlineStr">
         <is>
-          <t>Khách mua sắm tùy hứng / hơn nữa / thích quà tặng kèm</t>
+          <t>Khách mua sắm tùy hứng / hơn thế nữa / thích quà tặng kèm</t>
         </is>
       </c>
       <c r="K60" s="9" t="inlineStr">
         <is>
+          <t>3 cụm</t>
+        </is>
+      </c>
+      <c r="L60" s="9" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L60" s="11" t="inlineStr">
+      <c r="M60" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -9070,20 +10045,25 @@
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>cash-burning war / therefore / bottomless pit / swallow capital</t>
+          <t>cash-burning war / therefore now / bottomless pit / swallow capital</t>
         </is>
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>Trò chơi đốt tiền / do đó / hố sâu không đáy / nuốt trọn nguồn vốn</t>
+          <t>Trò chơi đốt tiền / do đó cho nên / hố sâu không đáy / nuốt trọn nguồn vốn</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
+          <t>4 cụm</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L61" s="7" t="inlineStr">
+      <c r="M61" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -9120,20 +10100,25 @@
       </c>
       <c r="I62" s="11" t="inlineStr">
         <is>
-          <t>aggressive price cuts / although / double-edged blade / erode profit margins</t>
+          <t>aggressive price cuts / although now / double-edged blade / erode profit margins</t>
         </is>
       </c>
       <c r="J62" s="11" t="inlineStr">
         <is>
-          <t>Giá cả cạnh tranh / mặc dù / con dao hai lưỡi / bào mòn lợi nhuận</t>
+          <t>Giá cả cạnh tranh / mặc dù vậy / con dao hai lưỡi / bào mòn lợi nhuận</t>
         </is>
       </c>
       <c r="K62" s="9" t="inlineStr">
         <is>
+          <t>4 cụm</t>
+        </is>
+      </c>
+      <c r="L62" s="9" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L62" s="11" t="inlineStr">
+      <c r="M62" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -9170,20 +10155,25 @@
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>Why / moreover / shopaholic instinct / overspend wildly</t>
+          <t>Why now / moreover now / shopaholic instinct / overspend wildly</t>
         </is>
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>Vì sao / hơn nữa / con nghiện mua sắm / vung tay quá trán</t>
+          <t>Lý do vì sao / hơn thế nữa / con nghiện mua sắm / vung tay quá trán</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
+          <t>4 cụm</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L63" s="7" t="inlineStr">
+      <c r="M63" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -9220,20 +10210,25 @@
       </c>
       <c r="I64" s="11" t="inlineStr">
         <is>
-          <t>window shopping stroll / then / sweet bait / trigger instant buy</t>
+          <t>window shopping stroll / then now / sweet bait / trigger instant buy</t>
         </is>
       </c>
       <c r="J64" s="11" t="inlineStr">
         <is>
-          <t>Đi lượn lờ ngắm đồ / sau đó / mồi câu hấp dẫn / khiến chốt đơn ngay</t>
+          <t>Đi lượn lờ ngắm đồ / sau đó liền / mồi câu hấp dẫn / khiến chốt đơn ngay</t>
         </is>
       </c>
       <c r="K64" s="9" t="inlineStr">
         <is>
+          <t>4 cụm</t>
+        </is>
+      </c>
+      <c r="L64" s="9" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L64" s="11" t="inlineStr">
+      <c r="M64" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -9270,7 +10265,7 @@
       </c>
       <c r="I65" s="7" t="inlineStr">
         <is>
-          <t>stuffed cart / instead / FOMO fever / rush to checkout</t>
+          <t>stuffed cart / instead of that / FOMO fever / rush to checkout</t>
         </is>
       </c>
       <c r="J65" s="7" t="inlineStr">
@@ -9280,10 +10275,15 @@
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
+          <t>4 cụm</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L65" s="7" t="inlineStr">
+      <c r="M65" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -9320,20 +10320,25 @@
       </c>
       <c r="I66" s="11" t="inlineStr">
         <is>
-          <t>How long / if / data leak breach / lose trust entirely</t>
+          <t>How long / if now / data leak breach / lose trust entirely</t>
         </is>
       </c>
       <c r="J66" s="11" t="inlineStr">
         <is>
-          <t>Bao lâu / nếu / rò rỉ dữ liệu / mất hết uy tín</t>
+          <t>Bao lâu / nếu không cẩn thận / rò rỉ dữ liệu / mất hết uy tín</t>
         </is>
       </c>
       <c r="K66" s="9" t="inlineStr">
         <is>
+          <t>4 cụm</t>
+        </is>
+      </c>
+      <c r="L66" s="9" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L66" s="11" t="inlineStr">
+      <c r="M66" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -9380,10 +10385,15 @@
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
+          <t>2 cụm</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L67" s="7" t="inlineStr">
+      <c r="M67" s="7" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -9420,20 +10430,25 @@
       </c>
       <c r="I68" s="11" t="inlineStr">
         <is>
-          <t>window shopping / unwind</t>
+          <t>window shopping / unwind now</t>
         </is>
       </c>
       <c r="J68" s="11" t="inlineStr">
         <is>
-          <t>Đi lượn lờ ngó nghiêng / xả stress</t>
+          <t>Đi lượn lờ ngó nghiêng / giải tỏa căng thẳng</t>
         </is>
       </c>
       <c r="K68" s="9" t="inlineStr">
         <is>
+          <t>2 cụm</t>
+        </is>
+      </c>
+      <c r="L68" s="9" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L68" s="11" t="inlineStr">
+      <c r="M68" s="11" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -9480,10 +10495,15 @@
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
+          <t>2 cụm</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L69" s="7" t="inlineStr">
+      <c r="M69" s="7" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -9525,15 +10545,20 @@
       </c>
       <c r="J70" s="11" t="inlineStr">
         <is>
-          <t>Khách mua sắm tùy hứng / hơn nữa / thích quà tặng kèm</t>
+          <t>Khách mua sắm tùy hứng / hơn thế nữa / thích quà tặng kèm</t>
         </is>
       </c>
       <c r="K70" s="9" t="inlineStr">
         <is>
+          <t>3 cụm</t>
+        </is>
+      </c>
+      <c r="L70" s="9" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L70" s="11" t="inlineStr">
+      <c r="M70" s="11" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -9570,20 +10595,25 @@
       </c>
       <c r="I71" s="7" t="inlineStr">
         <is>
-          <t>window shoppers / then / buy online later</t>
+          <t>window shoppers / then now / buy online later</t>
         </is>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>Người dạo phố ngắm đồ / sau đó / quay lại mua online</t>
+          <t>Người dạo phố ngắm đồ / sau đó liền / quay lại mua online</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
+          <t>3 cụm</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L71" s="7" t="inlineStr">
+      <c r="M71" s="7" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -9625,15 +10655,20 @@
       </c>
       <c r="J72" s="11" t="inlineStr">
         <is>
-          <t>Nền tảng mua bán / ví dụ / tích hợp livestream</t>
+          <t>Nền tảng mua bán / ví dụ như / tích hợp livestream</t>
         </is>
       </c>
       <c r="K72" s="9" t="inlineStr">
         <is>
+          <t>3 cụm</t>
+        </is>
+      </c>
+      <c r="L72" s="9" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L72" s="11" t="inlineStr">
+      <c r="M72" s="11" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -9670,20 +10705,25 @@
       </c>
       <c r="I73" s="7" t="inlineStr">
         <is>
-          <t>Why / moreover / shopaholic instinct / overspend wildly</t>
+          <t>Why now / moreover now / shopaholic instinct / overspend wildly</t>
         </is>
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>Vì sao / hơn nữa / con nghiện mua sắm / vung tay quá trán</t>
+          <t>Lý do vì sao / hơn thế nữa / con nghiện mua sắm / vung tay quá trán</t>
         </is>
       </c>
       <c r="K73" s="5" t="inlineStr">
         <is>
+          <t>4 cụm</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L73" s="7" t="inlineStr">
+      <c r="M73" s="7" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -9720,20 +10760,25 @@
       </c>
       <c r="I74" s="11" t="inlineStr">
         <is>
-          <t>window shopping stroll / then / sweet bait / trigger instant buy</t>
+          <t>window shopping stroll / then now / sweet bait / trigger instant buy</t>
         </is>
       </c>
       <c r="J74" s="11" t="inlineStr">
         <is>
-          <t>Đi lượn lờ ngắm đồ / sau đó / mồi câu hấp dẫn / khiến chốt đơn ngay</t>
+          <t>Đi lượn lờ ngắm đồ / sau đó liền / mồi câu hấp dẫn / khiến chốt đơn ngay</t>
         </is>
       </c>
       <c r="K74" s="9" t="inlineStr">
         <is>
+          <t>4 cụm</t>
+        </is>
+      </c>
+      <c r="L74" s="9" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L74" s="11" t="inlineStr">
+      <c r="M74" s="11" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -9770,7 +10815,7 @@
       </c>
       <c r="I75" s="7" t="inlineStr">
         <is>
-          <t>stuffed cart / instead / FOMO fever / rush to checkout</t>
+          <t>stuffed cart / instead of that / FOMO fever / rush to checkout</t>
         </is>
       </c>
       <c r="J75" s="7" t="inlineStr">
@@ -9780,10 +10825,15 @@
       </c>
       <c r="K75" s="5" t="inlineStr">
         <is>
+          <t>4 cụm</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L75" s="7" t="inlineStr">
+      <c r="M75" s="7" t="inlineStr">
         <is>
           <t>google/vi-VN-Neural2-A</t>
         </is>
@@ -9820,20 +10870,25 @@
       </c>
       <c r="I76" s="11" t="inlineStr">
         <is>
-          <t>shopping cart / overflowing</t>
+          <t>shopping cart / overflowing now</t>
         </is>
       </c>
       <c r="J76" s="11" t="inlineStr">
         <is>
-          <t>Giỏ hàng trực tuyến / chất đầy ắp</t>
+          <t>Giỏ hàng trực tuyến / chất đầy ắp giỏ</t>
         </is>
       </c>
       <c r="K76" s="9" t="inlineStr">
         <is>
+          <t>2 cụm</t>
+        </is>
+      </c>
+      <c r="L76" s="9" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L76" s="11" t="inlineStr">
+      <c r="M76" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -9870,20 +10925,25 @@
       </c>
       <c r="I77" s="7" t="inlineStr">
         <is>
-          <t>sales funnel / optimized</t>
+          <t>sales funnel / optimized now</t>
         </is>
       </c>
       <c r="J77" s="7" t="inlineStr">
         <is>
-          <t>Phễu bán hàng / tối ưu hóa</t>
+          <t>Phễu bán hàng / tối ưu hóa phễu</t>
         </is>
       </c>
       <c r="K77" s="5" t="inlineStr">
         <is>
+          <t>2 cụm</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L77" s="7" t="inlineStr">
+      <c r="M77" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -9920,20 +10980,25 @@
       </c>
       <c r="I78" s="11" t="inlineStr">
         <is>
-          <t>conversion rate / skyrocket</t>
+          <t>conversion rate / skyrocket now</t>
         </is>
       </c>
       <c r="J78" s="11" t="inlineStr">
         <is>
-          <t>Tỉ lệ chuyển đổi đơn / tăng vọt</t>
+          <t>Tỉ lệ chuyển đổi đơn / tăng vọt kỷ lục</t>
         </is>
       </c>
       <c r="K78" s="9" t="inlineStr">
         <is>
+          <t>2 cụm</t>
+        </is>
+      </c>
+      <c r="L78" s="9" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L78" s="11" t="inlineStr">
+      <c r="M78" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -9975,15 +11040,20 @@
       </c>
       <c r="J79" s="7" t="inlineStr">
         <is>
-          <t>Sản phẩm trong giỏ hàng / miễn là / còn đủ số lượng</t>
+          <t>Sản phẩm trong giỏ hàng / miễn là như vậy / còn đủ số lượng</t>
         </is>
       </c>
       <c r="K79" s="5" t="inlineStr">
         <is>
+          <t>3 cụm</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L79" s="7" t="inlineStr">
+      <c r="M79" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -10020,20 +11090,25 @@
       </c>
       <c r="I80" s="11" t="inlineStr">
         <is>
-          <t>funnel optimization / eventually / double sales</t>
+          <t>funnel optimization / eventually now / double sales</t>
         </is>
       </c>
       <c r="J80" s="11" t="inlineStr">
         <is>
-          <t>Tối ưu phễu chuyển đổi / sau cùng / nhân đôi doanh thu</t>
+          <t>Tối ưu phễu chuyển đổi / sau cùng thì / nhân đôi doanh thu</t>
         </is>
       </c>
       <c r="K80" s="9" t="inlineStr">
         <is>
+          <t>3 cụm</t>
+        </is>
+      </c>
+      <c r="L80" s="9" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L80" s="11" t="inlineStr">
+      <c r="M80" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -10070,20 +11145,25 @@
       </c>
       <c r="I81" s="7" t="inlineStr">
         <is>
-          <t>cashless payments / because / supremely convenient</t>
+          <t>cashless payments / because now / supremely convenient</t>
         </is>
       </c>
       <c r="J81" s="7" t="inlineStr">
         <is>
-          <t>Giao dịch không tiền mặt / bởi vì / tiện lợi vượt trội</t>
+          <t>Giao dịch không tiền mặt / bởi vì thế / tiện lợi vượt trội</t>
         </is>
       </c>
       <c r="K81" s="5" t="inlineStr">
         <is>
+          <t>3 cụm</t>
+        </is>
+      </c>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L81" s="7" t="inlineStr">
+      <c r="M81" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -10120,20 +11200,25 @@
       </c>
       <c r="I82" s="11" t="inlineStr">
         <is>
-          <t>How long / if / data leak breach / lose trust entirely</t>
+          <t>How long / if now / data leak breach / lose trust entirely</t>
         </is>
       </c>
       <c r="J82" s="11" t="inlineStr">
         <is>
-          <t>Bao lâu / nếu / rò rỉ dữ liệu / mất hết uy tín</t>
+          <t>Bao lâu / nếu không cẩn thận / rò rỉ dữ liệu / mất hết uy tín</t>
         </is>
       </c>
       <c r="K82" s="9" t="inlineStr">
         <is>
+          <t>4 cụm</t>
+        </is>
+      </c>
+      <c r="L82" s="9" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L82" s="11" t="inlineStr">
+      <c r="M82" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -10175,15 +11260,20 @@
       </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>Phễu bán hàng hiện đại / cho nên / cỗ máy in tiền / hoạt động tự động</t>
+          <t>Phễu bán hàng hiện đại / cho nên vì thế / cỗ máy in tiền / hoạt động tự động</t>
         </is>
       </c>
       <c r="K83" s="5" t="inlineStr">
         <is>
+          <t>4 cụm</t>
+        </is>
+      </c>
+      <c r="L83" s="5" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L83" s="7" t="inlineStr">
+      <c r="M83" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -10225,15 +11315,20 @@
       </c>
       <c r="J84" s="11" t="inlineStr">
         <is>
-          <t>Tỉ lệ chuyển đổi đơn / trái lại / thước đo sinh tử / quyết định sống còn</t>
+          <t>Tỉ lệ chuyển đổi đơn / trái lại hoàn toàn / thước đo sinh tử / quyết định sống còn</t>
         </is>
       </c>
       <c r="K84" s="9" t="inlineStr">
         <is>
+          <t>4 cụm</t>
+        </is>
+      </c>
+      <c r="L84" s="9" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L84" s="11" t="inlineStr">
+      <c r="M84" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -10275,15 +11370,20 @@
       </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>Mã miễn phí giao hàng / miễn là / cú hích tâm lý / thuyết phục khách mua</t>
+          <t>Mã miễn phí giao hàng / miễn là như vậy / cú hích tâm lý / thuyết phục khách mua</t>
         </is>
       </c>
       <c r="K85" s="5" t="inlineStr">
         <is>
+          <t>4 cụm</t>
+        </is>
+      </c>
+      <c r="L85" s="5" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L85" s="7" t="inlineStr">
+      <c r="M85" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -10320,20 +11420,25 @@
       </c>
       <c r="I86" s="11" t="inlineStr">
         <is>
-          <t>superfast delivery / next / killer feature / crush competition</t>
+          <t>superfast delivery / next now / killer feature / crush competition</t>
         </is>
       </c>
       <c r="J86" s="11" t="inlineStr">
         <is>
-          <t>Giao hàng hỏa tốc / tiếp theo / vũ khí sát thương / đánh bạt đối thủ</t>
+          <t>Giao hàng hỏa tốc / tiếp theo đó / vũ khí sát thương / đánh bạt đối thủ</t>
         </is>
       </c>
       <c r="K86" s="9" t="inlineStr">
         <is>
+          <t>4 cụm</t>
+        </is>
+      </c>
+      <c r="L86" s="9" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L86" s="11" t="inlineStr">
+      <c r="M86" s="11" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
@@ -10370,20 +11475,25 @@
       </c>
       <c r="I87" s="7" t="inlineStr">
         <is>
-          <t>Where / meanwhile / promised land / rural e-commerce</t>
+          <t>Where now / meanwhile now / promised land / rural e-commerce</t>
         </is>
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>Ở đâu / đồng thời / vùng đất hứa / thương mại nông thôn</t>
+          <t>ở bất cứ đâu / đồng thời cùng lúc / vùng đất hứa / thương mại nông thôn</t>
         </is>
       </c>
       <c r="K87" s="5" t="inlineStr">
         <is>
+          <t>4 cụm</t>
+        </is>
+      </c>
+      <c r="L87" s="5" t="inlineStr">
+        <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="L87" s="7" t="inlineStr">
+      <c r="M87" s="7" t="inlineStr">
         <is>
           <t>google/en-US-Neural2-F</t>
         </is>
